--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
@@ -943,9 +943,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7">
+      <c r="A2" s="7" t="str">
         <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v/>
+        <v>Painel de 17/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -983,27 +983,27 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="16">
         <f>COUNTIF(Tarefas!$L$4:$L$303,"Atrasada")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="17">
         <f>COUNTIF(Tarefas!$L$4:$L$303,"Hoje")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="18">
         <f>COUNTIF(Tarefas!$L$4:$L$303,"Esta semana")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F5" s="13" t="n"/>
       <c r="G5" s="18">
         <f>COUNTIFS(Tarefas!$B$4:$B$303,"&lt;&gt;",Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="H5" s="13" t="n"/>
       <c r="I5" s="19">
         <f>COUNTIF(Tarefas!$I$4:$I$303,"Feito")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J5" s="15" t="n"/>
     </row>
@@ -1062,348 +1062,348 @@
       <c r="A10" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Enviar relatório de setembro para a diretoria</v>
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="23">
+        <v>46281.0</v>
+      </c>
+      <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="23">
+        <v>Atrasada</v>
+      </c>
+      <c r="E10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F10" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G10" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Revisar proposta comercial da Aurora</v>
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="23">
+        <v>46282.0</v>
+      </c>
+      <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
+        <v>Hoje</v>
+      </c>
+      <c r="E11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F11" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G11" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Responder pesquisa de clima</v>
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="23">
+        <v>46280.0</v>
+      </c>
+      <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="23">
+        <v>Atrasada</v>
+      </c>
+      <c r="E12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
+        <v>Baixa</v>
+      </c>
+      <c r="F12" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G12" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Montar apresentação da reunião de quinta</v>
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="23">
+        <v>46283.0</v>
+      </c>
+      <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F13" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G13" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Aprovar arte do post de terça</v>
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="23">
+        <v>46283.0</v>
+      </c>
+      <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F14" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Carla</v>
       </c>
       <c r="G14" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Fechar pauta de outubro</v>
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="23">
+        <v>46285.0</v>
+      </c>
+      <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F15" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Carla</v>
       </c>
       <c r="G15" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Escrever e-mail de resultados para a Horizonte</v>
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="23">
+        <v>46286.0</v>
+      </c>
+      <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="24">
+        <v>Alta</v>
+      </c>
+      <c r="F16" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G16" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Atualizar planilha de leads</v>
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
+        <v>46283.0</v>
+      </c>
+      <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="24">
+        <v>Média</v>
+      </c>
+      <c r="F17" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Bruno</v>
       </c>
       <c r="G17" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Reunião de alinhamento com o Bruno</v>
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="23">
+        <v>46284.0</v>
+      </c>
+      <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
+        <v>Média</v>
+      </c>
+      <c r="F18" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G18" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Preparar orçamento do vídeo institucional</v>
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="23">
+        <v>46288.0</v>
+      </c>
+      <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
+        <v>Média</v>
+      </c>
+      <c r="F19" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G19" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Conferir faturas dos fornecedores</v>
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="23">
+        <v>46286.0</v>
+      </c>
+      <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="24">
+        <v>Baixa</v>
+      </c>
+      <c r="F20" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="G20" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$B$4:$B$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Organizar pasta de fotos do evento</v>
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="23">
+        <v>46287.0</v>
+      </c>
+      <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="23">
+        <v>Esta semana</v>
+      </c>
+      <c r="E21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$J$4:$J$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="24">
+        <v>Baixa</v>
+      </c>
+      <c r="F21" s="24" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$D$4:$D$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>Bruno</v>
       </c>
       <c r="G21" s="23">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$H$4:$H$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1448,197 +1448,197 @@
       <c r="H24" s="27" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="23">
+      <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>qui</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v/>
+        <v>46282.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D25" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="E25" s="28">
         <f>IF(Config!$B$6&gt;0,D25/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="F25" s="29" t="str">
         <f>REPT("█",ROUND(D25,0))&amp;IF(D25&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>██</v>
       </c>
       <c r="G25" s="24" t="n"/>
       <c r="H25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="23">
+      <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>sex</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v/>
+        <v>46283.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D26" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="E26" s="28">
         <f>IF(Config!$B$6&gt;0,D26/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F26" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="F26" s="29" t="str">
         <f>REPT("█",ROUND(D26,0))&amp;IF(D26&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>█████</v>
       </c>
       <c r="G26" s="24" t="n"/>
       <c r="H26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="23">
+      <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>sáb</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v/>
+        <v>46284.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D27" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E27" s="28">
         <f>IF(Config!$B$6&gt;0,D27/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F27" s="29">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F27" s="29" t="str">
         <f>REPT("█",ROUND(D27,0))&amp;IF(D27&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>█</v>
       </c>
       <c r="G27" s="24" t="n"/>
       <c r="H27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="23">
+      <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>dom</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v/>
+        <v>46285.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D28" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E28" s="28">
         <f>IF(Config!$B$6&gt;0,D28/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="29">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F28" s="29" t="str">
         <f>REPT("█",ROUND(D28,0))&amp;IF(D28&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>██</v>
       </c>
       <c r="G28" s="24" t="n"/>
       <c r="H28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="23">
+      <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>seg</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v/>
+        <v>46286.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D29" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E29" s="28">
         <f>IF(Config!$B$6&gt;0,D29/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F29" s="29">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F29" s="29" t="str">
         <f>REPT("█",ROUND(D29,0))&amp;IF(D29&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>██</v>
       </c>
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="23">
+      <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>ter</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v/>
+        <v>46287.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D30" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E30" s="28">
         <f>IF(Config!$B$6&gt;0,D30/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F30" s="29">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F30" s="29" t="str">
         <f>REPT("█",ROUND(D30,0))&amp;IF(D30&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>██</v>
       </c>
       <c r="G30" s="24" t="n"/>
       <c r="H30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="23">
+      <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v/>
+        <v>qua</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v/>
+        <v>46288.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D31" s="23">
         <f>SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E31" s="28">
         <f>IF(Config!$B$6&gt;0,D31/Config!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="29">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F31" s="29" t="str">
         <f>REPT("█",ROUND(D31,0))&amp;IF(D31&gt;Config!$B$6," ⚠ acima da capacidade","")</f>
-        <v/>
+        <v>██</v>
       </c>
       <c r="G31" s="24" t="n"/>
       <c r="H31" s="24" t="n"/>
@@ -1686,72 +1686,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="24" t="str">
         <f>IF(Config!$B$9="","",Config!$B$9)</f>
-        <v/>
+        <v>Ana (você)</v>
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="23">
         <f>IF(Config!$B$9="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$9,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;"))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D36" s="23">
         <f>IF(Config!$B$9="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$9,Tarefas!$L$4:$L$303,"Atrasada"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E36" s="23">
         <f>IF(Config!$B$9="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$9,Tarefas!$L$4:$L$303,"Hoje"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F36" s="23">
         <f>IF(Config!$B$9="","",SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$D$4:$D$303,Config!$B$9,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado"))</f>
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24">
+      <c r="A37" s="24" t="str">
         <f>IF(Config!$B$10="","",Config!$B$10)</f>
-        <v/>
+        <v>Bruno</v>
       </c>
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="23">
         <f>IF(Config!$B$10="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$10,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;"))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D37" s="23">
         <f>IF(Config!$B$10="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$10,Tarefas!$L$4:$L$303,"Atrasada"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E37" s="23">
         <f>IF(Config!$B$10="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$10,Tarefas!$L$4:$L$303,"Hoje"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F37" s="23">
         <f>IF(Config!$B$10="","",SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$D$4:$D$303,Config!$B$10,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado"))</f>
-        <v/>
+        <v>8.5</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24">
+      <c r="A38" s="24" t="str">
         <f>IF(Config!$B$11="","",Config!$B$11)</f>
-        <v/>
+        <v>Carla</v>
       </c>
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="23">
         <f>IF(Config!$B$11="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$11,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D38" s="23">
         <f>IF(Config!$B$11="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$11,Tarefas!$L$4:$L$303,"Atrasada"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E38" s="23">
         <f>IF(Config!$B$11="","",COUNTIFS(Tarefas!$D$4:$D$303,Config!$B$11,Tarefas!$L$4:$L$303,"Hoje"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="23">
         <f>IF(Config!$B$11="","",SUMIFS(Tarefas!$H$4:$H$303,Tarefas!$D$4:$D$303,Config!$B$11,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado"))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v/>
+        <v>46282.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
     <row r="4">
       <c r="A4" s="23">
         <f>IF(B4="","",ROW()-3)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v/>
+        <v>46281.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2248,21 +2248,21 @@
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="J4" s="24">
+      <c r="J4" s="24" t="str">
         <f>IF(B4="","",IF(F4*G4&gt;=6,"Alta",IF(F4*G4&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K4" s="23">
         <f>IF(OR(B4="",E4=""),"",E4-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="24">
+        <v>-1</v>
+      </c>
+      <c r="L4" s="24" t="str">
         <f>IF(B4="","",IF(OR(I4="Feito",I4="Cancelado"),I4,IF(E4="","Sem prazo",IF(K4&lt;0,"Atrasada",IF(K4=0,"Hoje",IF(K4&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Atrasada</v>
       </c>
       <c r="M4" s="39">
         <f>IF(OR(B4="",L4="Feito",L4="Cancelado",L4="Sem prazo",L4="Depois"),0,IF(L4="Atrasada",2000,IF(L4="Hoje",1500,500))+F4*G4*100+IF(K4&lt;0,MIN(-K4,30),10-K4)-ROW()/100000)</f>
-        <v/>
+        <v>2900.99996</v>
       </c>
       <c r="N4" s="36" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
     <row r="5">
       <c r="A5" s="23">
         <f>IF(B5="","",ROW()-3)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v/>
+        <v>46282.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2308,21 +2308,21 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="24" t="str">
         <f>IF(B5="","",IF(F5*G5&gt;=6,"Alta",IF(F5*G5&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K5" s="23">
         <f>IF(OR(B5="",E5=""),"",E5-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="24">
+        <v>0</v>
+      </c>
+      <c r="L5" s="24" t="str">
         <f>IF(B5="","",IF(OR(I5="Feito",I5="Cancelado"),I5,IF(E5="","Sem prazo",IF(K5&lt;0,"Atrasada",IF(K5=0,"Hoje",IF(K5&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="M5" s="39">
         <f>IF(OR(B5="",L5="Feito",L5="Cancelado",L5="Sem prazo",L5="Depois"),0,IF(L5="Atrasada",2000,IF(L5="Hoje",1500,500))+F5*G5*100+IF(K5&lt;0,MIN(-K5,30),10-K5)-ROW()/100000)</f>
-        <v/>
+        <v>2109.99995</v>
       </c>
       <c r="N5" s="36" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
     <row r="6">
       <c r="A6" s="23">
         <f>IF(B6="","",ROW()-3)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v/>
+        <v>46280.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2368,28 +2368,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="24" t="str">
         <f>IF(B6="","",IF(F6*G6&gt;=6,"Alta",IF(F6*G6&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K6" s="23">
         <f>IF(OR(B6="",E6=""),"",E6-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="24">
+        <v>-2</v>
+      </c>
+      <c r="L6" s="24" t="str">
         <f>IF(B6="","",IF(OR(I6="Feito",I6="Cancelado"),I6,IF(E6="","Sem prazo",IF(K6&lt;0,"Atrasada",IF(K6=0,"Hoje",IF(K6&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Atrasada</v>
       </c>
       <c r="M6" s="39">
         <f>IF(OR(B6="",L6="Feito",L6="Cancelado",L6="Sem prazo",L6="Depois"),0,IF(L6="Atrasada",2000,IF(L6="Hoje",1500,500))+F6*G6*100+IF(K6&lt;0,MIN(-K6,30),10-K6)-ROW()/100000)</f>
-        <v/>
+        <v>2101.99994</v>
       </c>
       <c r="N6" s="36" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="23">
         <f>IF(B7="","",ROW()-3)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v/>
+        <v>46283.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2424,21 +2424,21 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="24" t="str">
         <f>IF(B7="","",IF(F7*G7&gt;=6,"Alta",IF(F7*G7&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K7" s="23">
         <f>IF(OR(B7="",E7=""),"",E7-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="24">
+        <v>1</v>
+      </c>
+      <c r="L7" s="24" t="str">
         <f>IF(B7="","",IF(OR(I7="Feito",I7="Cancelado"),I7,IF(E7="","Sem prazo",IF(K7&lt;0,"Atrasada",IF(K7=0,"Hoje",IF(K7&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M7" s="39">
         <f>IF(OR(B7="",L7="Feito",L7="Cancelado",L7="Sem prazo",L7="Depois"),0,IF(L7="Atrasada",2000,IF(L7="Hoje",1500,500))+F7*G7*100+IF(K7&lt;0,MIN(-K7,30),10-K7)-ROW()/100000)</f>
-        <v/>
+        <v>1408.99993</v>
       </c>
       <c r="N7" s="36" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
     <row r="8">
       <c r="A8" s="23">
         <f>IF(B8="","",ROW()-3)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v/>
+        <v>46283.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2484,28 +2484,28 @@
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="24" t="str">
         <f>IF(B8="","",IF(F8*G8&gt;=6,"Alta",IF(F8*G8&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K8" s="23">
         <f>IF(OR(B8="",E8=""),"",E8-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="24">
+        <v>1</v>
+      </c>
+      <c r="L8" s="24" t="str">
         <f>IF(B8="","",IF(OR(I8="Feito",I8="Cancelado"),I8,IF(E8="","Sem prazo",IF(K8&lt;0,"Atrasada",IF(K8=0,"Hoje",IF(K8&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M8" s="39">
         <f>IF(OR(B8="",L8="Feito",L8="Cancelado",L8="Sem prazo",L8="Depois"),0,IF(L8="Atrasada",2000,IF(L8="Hoje",1500,500))+F8*G8*100+IF(K8&lt;0,MIN(-K8,30),10-K8)-ROW()/100000)</f>
-        <v/>
+        <v>908.99992</v>
       </c>
       <c r="N8" s="36" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="23">
         <f>IF(B9="","",ROW()-3)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v/>
+        <v>46283.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2540,28 +2540,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="24" t="str">
         <f>IF(B9="","",IF(F9*G9&gt;=6,"Alta",IF(F9*G9&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K9" s="23">
         <f>IF(OR(B9="",E9=""),"",E9-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L9" s="24">
+        <v>1</v>
+      </c>
+      <c r="L9" s="24" t="str">
         <f>IF(B9="","",IF(OR(I9="Feito",I9="Cancelado"),I9,IF(E9="","Sem prazo",IF(K9&lt;0,"Atrasada",IF(K9=0,"Hoje",IF(K9&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M9" s="39">
         <f>IF(OR(B9="",L9="Feito",L9="Cancelado",L9="Sem prazo",L9="Depois"),0,IF(L9="Atrasada",2000,IF(L9="Hoje",1500,500))+F9*G9*100+IF(K9&lt;0,MIN(-K9,30),10-K9)-ROW()/100000)</f>
-        <v/>
+        <v>1108.99991</v>
       </c>
       <c r="N9" s="36" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23">
         <f>IF(B10="","",ROW()-3)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v/>
+        <v>46284.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2596,21 +2596,21 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="24" t="str">
         <f>IF(B10="","",IF(F10*G10&gt;=6,"Alta",IF(F10*G10&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K10" s="23">
         <f>IF(OR(B10="",E10=""),"",E10-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L10" s="24">
+        <v>2</v>
+      </c>
+      <c r="L10" s="24" t="str">
         <f>IF(B10="","",IF(OR(I10="Feito",I10="Cancelado"),I10,IF(E10="","Sem prazo",IF(K10&lt;0,"Atrasada",IF(K10=0,"Hoje",IF(K10&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M10" s="39">
         <f>IF(OR(B10="",L10="Feito",L10="Cancelado",L10="Sem prazo",L10="Depois"),0,IF(L10="Atrasada",2000,IF(L10="Hoje",1500,500))+F10*G10*100+IF(K10&lt;0,MIN(-K10,30),10-K10)-ROW()/100000)</f>
-        <v/>
+        <v>907.9999</v>
       </c>
       <c r="N10" s="36" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
     <row r="11">
       <c r="A11" s="23">
         <f>IF(B11="","",ROW()-3)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v/>
+        <v>46285.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2656,28 +2656,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="24" t="str">
         <f>IF(B11="","",IF(F11*G11&gt;=6,"Alta",IF(F11*G11&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K11" s="23">
         <f>IF(OR(B11="",E11=""),"",E11-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L11" s="24">
+        <v>3</v>
+      </c>
+      <c r="L11" s="24" t="str">
         <f>IF(B11="","",IF(OR(I11="Feito",I11="Cancelado"),I11,IF(E11="","Sem prazo",IF(K11&lt;0,"Atrasada",IF(K11=0,"Hoje",IF(K11&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M11" s="39">
         <f>IF(OR(B11="",L11="Feito",L11="Cancelado",L11="Sem prazo",L11="Depois"),0,IF(L11="Atrasada",2000,IF(L11="Hoje",1500,500))+F11*G11*100+IF(K11&lt;0,MIN(-K11,30),10-K11)-ROW()/100000)</f>
-        <v/>
+        <v>1106.99989</v>
       </c>
       <c r="N11" s="36" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="23">
         <f>IF(B12="","",ROW()-3)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v/>
+        <v>46286.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2712,28 +2712,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="24" t="str">
         <f>IF(B12="","",IF(F12*G12&gt;=6,"Alta",IF(F12*G12&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K12" s="23">
         <f>IF(OR(B12="",E12=""),"",E12-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L12" s="24">
+        <v>4</v>
+      </c>
+      <c r="L12" s="24" t="str">
         <f>IF(B12="","",IF(OR(I12="Feito",I12="Cancelado"),I12,IF(E12="","Sem prazo",IF(K12&lt;0,"Atrasada",IF(K12=0,"Hoje",IF(K12&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M12" s="39">
         <f>IF(OR(B12="",L12="Feito",L12="Cancelado",L12="Sem prazo",L12="Depois"),0,IF(L12="Atrasada",2000,IF(L12="Hoje",1500,500))+F12*G12*100+IF(K12&lt;0,MIN(-K12,30),10-K12)-ROW()/100000)</f>
-        <v/>
+        <v>705.99988</v>
       </c>
       <c r="N12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="23">
         <f>IF(B13="","",ROW()-3)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v/>
+        <v>46286.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2768,21 +2768,21 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="24" t="str">
         <f>IF(B13="","",IF(F13*G13&gt;=6,"Alta",IF(F13*G13&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K13" s="23">
         <f>IF(OR(B13="",E13=""),"",E13-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L13" s="24">
+        <v>4</v>
+      </c>
+      <c r="L13" s="24" t="str">
         <f>IF(B13="","",IF(OR(I13="Feito",I13="Cancelado"),I13,IF(E13="","Sem prazo",IF(K13&lt;0,"Atrasada",IF(K13=0,"Hoje",IF(K13&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M13" s="39">
         <f>IF(OR(B13="",L13="Feito",L13="Cancelado",L13="Sem prazo",L13="Depois"),0,IF(L13="Atrasada",2000,IF(L13="Hoje",1500,500))+F13*G13*100+IF(K13&lt;0,MIN(-K13,30),10-K13)-ROW()/100000)</f>
-        <v/>
+        <v>1105.99987</v>
       </c>
       <c r="N13" s="36" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
     <row r="14">
       <c r="A14" s="23">
         <f>IF(B14="","",ROW()-3)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v/>
+        <v>46287.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2828,28 +2828,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="24" t="str">
         <f>IF(B14="","",IF(F14*G14&gt;=6,"Alta",IF(F14*G14&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K14" s="23">
         <f>IF(OR(B14="",E14=""),"",E14-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L14" s="24">
+        <v>5</v>
+      </c>
+      <c r="L14" s="24" t="str">
         <f>IF(B14="","",IF(OR(I14="Feito",I14="Cancelado"),I14,IF(E14="","Sem prazo",IF(K14&lt;0,"Atrasada",IF(K14=0,"Hoje",IF(K14&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M14" s="39">
         <f>IF(OR(B14="",L14="Feito",L14="Cancelado",L14="Sem prazo",L14="Depois"),0,IF(L14="Atrasada",2000,IF(L14="Hoje",1500,500))+F14*G14*100+IF(K14&lt;0,MIN(-K14,30),10-K14)-ROW()/100000)</f>
-        <v/>
+        <v>604.99986</v>
       </c>
       <c r="N14" s="36" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="23">
         <f>IF(B15="","",ROW()-3)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="B15" s="36" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v/>
+        <v>46288.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2884,28 +2884,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="24" t="str">
         <f>IF(B15="","",IF(F15*G15&gt;=6,"Alta",IF(F15*G15&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K15" s="23">
         <f>IF(OR(B15="",E15=""),"",E15-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L15" s="24">
+        <v>6</v>
+      </c>
+      <c r="L15" s="24" t="str">
         <f>IF(B15="","",IF(OR(I15="Feito",I15="Cancelado"),I15,IF(E15="","Sem prazo",IF(K15&lt;0,"Atrasada",IF(K15=0,"Hoje",IF(K15&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Esta semana</v>
       </c>
       <c r="M15" s="39">
         <f>IF(OR(B15="",L15="Feito",L15="Cancelado",L15="Sem prazo",L15="Depois"),0,IF(L15="Atrasada",2000,IF(L15="Hoje",1500,500))+F15*G15*100+IF(K15&lt;0,MIN(-K15,30),10-K15)-ROW()/100000)</f>
-        <v/>
+        <v>803.99985</v>
       </c>
       <c r="N15" s="36" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23">
         <f>IF(B16="","",ROW()-3)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="B16" s="36" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v/>
+        <v>46289.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2940,28 +2940,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="24" t="str">
         <f>IF(B16="","",IF(F16*G16&gt;=6,"Alta",IF(F16*G16&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K16" s="23">
         <f>IF(OR(B16="",E16=""),"",E16-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L16" s="24">
+        <v>7</v>
+      </c>
+      <c r="L16" s="24" t="str">
         <f>IF(B16="","",IF(OR(I16="Feito",I16="Cancelado"),I16,IF(E16="","Sem prazo",IF(K16&lt;0,"Atrasada",IF(K16=0,"Hoje",IF(K16&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="M16" s="39">
         <f>IF(OR(B16="",L16="Feito",L16="Cancelado",L16="Sem prazo",L16="Depois"),0,IF(L16="Atrasada",2000,IF(L16="Hoje",1500,500))+F16*G16*100+IF(K16&lt;0,MIN(-K16,30),10-K16)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N16" s="36" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23">
         <f>IF(B17="","",ROW()-3)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="B17" s="36" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v/>
+        <v>46273.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -2996,28 +2996,28 @@
           <t>Feito</t>
         </is>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="24" t="str">
         <f>IF(B17="","",IF(F17*G17&gt;=6,"Alta",IF(F17*G17&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Alta</v>
       </c>
       <c r="K17" s="23">
         <f>IF(OR(B17="",E17=""),"",E17-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L17" s="24">
+        <v>-9</v>
+      </c>
+      <c r="L17" s="24" t="str">
         <f>IF(B17="","",IF(OR(I17="Feito",I17="Cancelado"),I17,IF(E17="","Sem prazo",IF(K17&lt;0,"Atrasada",IF(K17=0,"Hoje",IF(K17&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Feito</v>
       </c>
       <c r="M17" s="39">
         <f>IF(OR(B17="",L17="Feito",L17="Cancelado",L17="Sem prazo",L17="Depois"),0,IF(L17="Atrasada",2000,IF(L17="Hoje",1500,500))+F17*G17*100+IF(K17&lt;0,MIN(-K17,30),10-K17)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N17" s="36" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="23">
         <f>IF(B18="","",ROW()-3)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="B18" s="36" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v/>
+        <v>46292.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3052,28 +3052,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="24" t="str">
         <f>IF(B18="","",IF(F18*G18&gt;=6,"Alta",IF(F18*G18&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K18" s="23">
         <f>IF(OR(B18="",E18=""),"",E18-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L18" s="24">
+        <v>10</v>
+      </c>
+      <c r="L18" s="24" t="str">
         <f>IF(B18="","",IF(OR(I18="Feito",I18="Cancelado"),I18,IF(E18="","Sem prazo",IF(K18&lt;0,"Atrasada",IF(K18=0,"Hoje",IF(K18&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="M18" s="39">
         <f>IF(OR(B18="",L18="Feito",L18="Cancelado",L18="Sem prazo",L18="Depois"),0,IF(L18="Atrasada",2000,IF(L18="Hoje",1500,500))+F18*G18*100+IF(K18&lt;0,MIN(-K18,30),10-K18)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N18" s="36" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="23">
         <f>IF(B19="","",ROW()-3)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="B19" s="36" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v/>
+        <v>46295.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3108,28 +3108,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="24" t="str">
         <f>IF(B19="","",IF(F19*G19&gt;=6,"Alta",IF(F19*G19&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K19" s="23">
         <f>IF(OR(B19="",E19=""),"",E19-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
+        <v>13</v>
+      </c>
+      <c r="L19" s="24" t="str">
         <f>IF(B19="","",IF(OR(I19="Feito",I19="Cancelado"),I19,IF(E19="","Sem prazo",IF(K19&lt;0,"Atrasada",IF(K19=0,"Hoje",IF(K19&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="M19" s="39">
         <f>IF(OR(B19="",L19="Feito",L19="Cancelado",L19="Sem prazo",L19="Depois"),0,IF(L19="Atrasada",2000,IF(L19="Hoje",1500,500))+F19*G19*100+IF(K19&lt;0,MIN(-K19,30),10-K19)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N19" s="36" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="23">
         <f>IF(B20="","",ROW()-3)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v/>
+        <v>46298.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3164,28 +3164,28 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="24" t="str">
         <f>IF(B20="","",IF(F20*G20&gt;=6,"Alta",IF(F20*G20&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K20" s="23">
         <f>IF(OR(B20="",E20=""),"",E20-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L20" s="24">
+        <v>16</v>
+      </c>
+      <c r="L20" s="24" t="str">
         <f>IF(B20="","",IF(OR(I20="Feito",I20="Cancelado"),I20,IF(E20="","Sem prazo",IF(K20&lt;0,"Atrasada",IF(K20=0,"Hoje",IF(K20&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="M20" s="39">
         <f>IF(OR(B20="",L20="Feito",L20="Cancelado",L20="Sem prazo",L20="Depois"),0,IF(L20="Atrasada",2000,IF(L20="Hoje",1500,500))+F20*G20*100+IF(K20&lt;0,MIN(-K20,30),10-K20)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N20" s="36" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="23">
         <f>IF(B21="","",ROW()-3)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="B21" s="36" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3220,21 +3220,21 @@
           <t>Cancelado</t>
         </is>
       </c>
-      <c r="J21" s="24">
+      <c r="J21" s="24" t="str">
         <f>IF(B21="","",IF(F21*G21&gt;=6,"Alta",IF(F21*G21&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K21" s="23">
         <f>IF(OR(B21="",E21=""),"",E21-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L21" s="24">
+        <v>-3</v>
+      </c>
+      <c r="L21" s="24" t="str">
         <f>IF(B21="","",IF(OR(I21="Feito",I21="Cancelado"),I21,IF(E21="","Sem prazo",IF(K21&lt;0,"Atrasada",IF(K21=0,"Hoje",IF(K21&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Cancelado</v>
       </c>
       <c r="M21" s="39">
         <f>IF(OR(B21="",L21="Feito",L21="Cancelado",L21="Sem prazo",L21="Depois"),0,IF(L21="Atrasada",2000,IF(L21="Hoje",1500,500))+F21*G21*100+IF(K21&lt;0,MIN(-K21,30),10-K21)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N21" s="36" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
     <row r="22">
       <c r="A22" s="23">
         <f>IF(B22="","",ROW()-3)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="B22" s="36" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="24" t="str">
         <f>IF(B22="","",IF(F22*G22&gt;=6,"Alta",IF(F22*G22&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Baixa</v>
       </c>
       <c r="K22" s="23">
         <f>IF(OR(B22="",E22=""),"",E22-Config!$B$4)</f>
         <v/>
       </c>
-      <c r="L22" s="24">
+      <c r="L22" s="24" t="str">
         <f>IF(B22="","",IF(OR(I22="Feito",I22="Cancelado"),I22,IF(E22="","Sem prazo",IF(K22&lt;0,"Atrasada",IF(K22=0,"Hoje",IF(K22&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Sem prazo</v>
       </c>
       <c r="M22" s="39">
         <f>IF(OR(B22="",L22="Feito",L22="Cancelado",L22="Sem prazo",L22="Depois"),0,IF(L22="Atrasada",2000,IF(L22="Hoje",1500,500))+F22*G22*100+IF(K22&lt;0,MIN(-K22,30),10-K22)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N22" s="36" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
     <row r="23">
       <c r="A23" s="23">
         <f>IF(B23="","",ROW()-3)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v/>
+        <v>46276.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>
@@ -3337,21 +3337,21 @@
           <t>Feito</t>
         </is>
       </c>
-      <c r="J23" s="24">
+      <c r="J23" s="24" t="str">
         <f>IF(B23="","",IF(F23*G23&gt;=6,"Alta",IF(F23*G23&gt;=3,"Média","Baixa")))</f>
-        <v/>
+        <v>Média</v>
       </c>
       <c r="K23" s="23">
         <f>IF(OR(B23="",E23=""),"",E23-Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="L23" s="24">
+        <v>-6</v>
+      </c>
+      <c r="L23" s="24" t="str">
         <f>IF(B23="","",IF(OR(I23="Feito",I23="Cancelado"),I23,IF(E23="","Sem prazo",IF(K23&lt;0,"Atrasada",IF(K23=0,"Hoje",IF(K23&lt;=6,"Esta semana","Depois"))))))</f>
-        <v/>
+        <v>Feito</v>
       </c>
       <c r="M23" s="39">
         <f>IF(OR(B23="",L23="Feito",L23="Cancelado",L23="Sem prazo",L23="Depois"),0,IF(L23="Atrasada",2000,IF(L23="Hoje",1500,500))+F23*G23*100+IF(K23&lt;0,MIN(-K23,30),10-K23)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N23" s="36" t="inlineStr"/>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="M24" s="39">
         <f>IF(OR(B24="",L24="Feito",L24="Cancelado",L24="Sem prazo",L24="Depois"),0,IF(L24="Atrasada",2000,IF(L24="Hoje",1500,500))+F24*G24*100+IF(K24&lt;0,MIN(-K24,30),10-K24)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N24" s="36" t="n"/>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="M25" s="39">
         <f>IF(OR(B25="",L25="Feito",L25="Cancelado",L25="Sem prazo",L25="Depois"),0,IF(L25="Atrasada",2000,IF(L25="Hoje",1500,500))+F25*G25*100+IF(K25&lt;0,MIN(-K25,30),10-K25)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N25" s="36" t="n"/>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M26" s="39">
         <f>IF(OR(B26="",L26="Feito",L26="Cancelado",L26="Sem prazo",L26="Depois"),0,IF(L26="Atrasada",2000,IF(L26="Hoje",1500,500))+F26*G26*100+IF(K26&lt;0,MIN(-K26,30),10-K26)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N26" s="36" t="n"/>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="M27" s="39">
         <f>IF(OR(B27="",L27="Feito",L27="Cancelado",L27="Sem prazo",L27="Depois"),0,IF(L27="Atrasada",2000,IF(L27="Hoje",1500,500))+F27*G27*100+IF(K27&lt;0,MIN(-K27,30),10-K27)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N27" s="36" t="n"/>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="M28" s="39">
         <f>IF(OR(B28="",L28="Feito",L28="Cancelado",L28="Sem prazo",L28="Depois"),0,IF(L28="Atrasada",2000,IF(L28="Hoje",1500,500))+F28*G28*100+IF(K28&lt;0,MIN(-K28,30),10-K28)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N28" s="36" t="n"/>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="M29" s="39">
         <f>IF(OR(B29="",L29="Feito",L29="Cancelado",L29="Sem prazo",L29="Depois"),0,IF(L29="Atrasada",2000,IF(L29="Hoje",1500,500))+F29*G29*100+IF(K29&lt;0,MIN(-K29,30),10-K29)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N29" s="36" t="n"/>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="M30" s="39">
         <f>IF(OR(B30="",L30="Feito",L30="Cancelado",L30="Sem prazo",L30="Depois"),0,IF(L30="Atrasada",2000,IF(L30="Hoje",1500,500))+F30*G30*100+IF(K30&lt;0,MIN(-K30,30),10-K30)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N30" s="36" t="n"/>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M31" s="39">
         <f>IF(OR(B31="",L31="Feito",L31="Cancelado",L31="Sem prazo",L31="Depois"),0,IF(L31="Atrasada",2000,IF(L31="Hoje",1500,500))+F31*G31*100+IF(K31&lt;0,MIN(-K31,30),10-K31)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N31" s="36" t="n"/>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="M32" s="39">
         <f>IF(OR(B32="",L32="Feito",L32="Cancelado",L32="Sem prazo",L32="Depois"),0,IF(L32="Atrasada",2000,IF(L32="Hoje",1500,500))+F32*G32*100+IF(K32&lt;0,MIN(-K32,30),10-K32)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N32" s="36" t="n"/>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M33" s="39">
         <f>IF(OR(B33="",L33="Feito",L33="Cancelado",L33="Sem prazo",L33="Depois"),0,IF(L33="Atrasada",2000,IF(L33="Hoje",1500,500))+F33*G33*100+IF(K33&lt;0,MIN(-K33,30),10-K33)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N33" s="36" t="n"/>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="M34" s="39">
         <f>IF(OR(B34="",L34="Feito",L34="Cancelado",L34="Sem prazo",L34="Depois"),0,IF(L34="Atrasada",2000,IF(L34="Hoje",1500,500))+F34*G34*100+IF(K34&lt;0,MIN(-K34,30),10-K34)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N34" s="36" t="n"/>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M35" s="39">
         <f>IF(OR(B35="",L35="Feito",L35="Cancelado",L35="Sem prazo",L35="Depois"),0,IF(L35="Atrasada",2000,IF(L35="Hoje",1500,500))+F35*G35*100+IF(K35&lt;0,MIN(-K35,30),10-K35)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N35" s="36" t="n"/>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="M36" s="39">
         <f>IF(OR(B36="",L36="Feito",L36="Cancelado",L36="Sem prazo",L36="Depois"),0,IF(L36="Atrasada",2000,IF(L36="Hoje",1500,500))+F36*G36*100+IF(K36&lt;0,MIN(-K36,30),10-K36)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N36" s="36" t="n"/>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="M37" s="39">
         <f>IF(OR(B37="",L37="Feito",L37="Cancelado",L37="Sem prazo",L37="Depois"),0,IF(L37="Atrasada",2000,IF(L37="Hoje",1500,500))+F37*G37*100+IF(K37&lt;0,MIN(-K37,30),10-K37)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N37" s="36" t="n"/>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="M38" s="39">
         <f>IF(OR(B38="",L38="Feito",L38="Cancelado",L38="Sem prazo",L38="Depois"),0,IF(L38="Atrasada",2000,IF(L38="Hoje",1500,500))+F38*G38*100+IF(K38&lt;0,MIN(-K38,30),10-K38)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N38" s="36" t="n"/>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="M39" s="39">
         <f>IF(OR(B39="",L39="Feito",L39="Cancelado",L39="Sem prazo",L39="Depois"),0,IF(L39="Atrasada",2000,IF(L39="Hoje",1500,500))+F39*G39*100+IF(K39&lt;0,MIN(-K39,30),10-K39)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N39" s="36" t="n"/>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="M40" s="39">
         <f>IF(OR(B40="",L40="Feito",L40="Cancelado",L40="Sem prazo",L40="Depois"),0,IF(L40="Atrasada",2000,IF(L40="Hoje",1500,500))+F40*G40*100+IF(K40&lt;0,MIN(-K40,30),10-K40)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N40" s="36" t="n"/>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="M41" s="39">
         <f>IF(OR(B41="",L41="Feito",L41="Cancelado",L41="Sem prazo",L41="Depois"),0,IF(L41="Atrasada",2000,IF(L41="Hoje",1500,500))+F41*G41*100+IF(K41&lt;0,MIN(-K41,30),10-K41)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N41" s="36" t="n"/>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="M42" s="39">
         <f>IF(OR(B42="",L42="Feito",L42="Cancelado",L42="Sem prazo",L42="Depois"),0,IF(L42="Atrasada",2000,IF(L42="Hoje",1500,500))+F42*G42*100+IF(K42&lt;0,MIN(-K42,30),10-K42)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N42" s="36" t="n"/>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="M43" s="39">
         <f>IF(OR(B43="",L43="Feito",L43="Cancelado",L43="Sem prazo",L43="Depois"),0,IF(L43="Atrasada",2000,IF(L43="Hoje",1500,500))+F43*G43*100+IF(K43&lt;0,MIN(-K43,30),10-K43)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N43" s="36" t="n"/>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="M44" s="39">
         <f>IF(OR(B44="",L44="Feito",L44="Cancelado",L44="Sem prazo",L44="Depois"),0,IF(L44="Atrasada",2000,IF(L44="Hoje",1500,500))+F44*G44*100+IF(K44&lt;0,MIN(-K44,30),10-K44)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N44" s="36" t="n"/>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="M45" s="39">
         <f>IF(OR(B45="",L45="Feito",L45="Cancelado",L45="Sem prazo",L45="Depois"),0,IF(L45="Atrasada",2000,IF(L45="Hoje",1500,500))+F45*G45*100+IF(K45&lt;0,MIN(-K45,30),10-K45)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N45" s="36" t="n"/>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="M46" s="39">
         <f>IF(OR(B46="",L46="Feito",L46="Cancelado",L46="Sem prazo",L46="Depois"),0,IF(L46="Atrasada",2000,IF(L46="Hoje",1500,500))+F46*G46*100+IF(K46&lt;0,MIN(-K46,30),10-K46)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N46" s="36" t="n"/>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M47" s="39">
         <f>IF(OR(B47="",L47="Feito",L47="Cancelado",L47="Sem prazo",L47="Depois"),0,IF(L47="Atrasada",2000,IF(L47="Hoje",1500,500))+F47*G47*100+IF(K47&lt;0,MIN(-K47,30),10-K47)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N47" s="36" t="n"/>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="M48" s="39">
         <f>IF(OR(B48="",L48="Feito",L48="Cancelado",L48="Sem prazo",L48="Depois"),0,IF(L48="Atrasada",2000,IF(L48="Hoje",1500,500))+F48*G48*100+IF(K48&lt;0,MIN(-K48,30),10-K48)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N48" s="36" t="n"/>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="M49" s="39">
         <f>IF(OR(B49="",L49="Feito",L49="Cancelado",L49="Sem prazo",L49="Depois"),0,IF(L49="Atrasada",2000,IF(L49="Hoje",1500,500))+F49*G49*100+IF(K49&lt;0,MIN(-K49,30),10-K49)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N49" s="36" t="n"/>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M50" s="39">
         <f>IF(OR(B50="",L50="Feito",L50="Cancelado",L50="Sem prazo",L50="Depois"),0,IF(L50="Atrasada",2000,IF(L50="Hoje",1500,500))+F50*G50*100+IF(K50&lt;0,MIN(-K50,30),10-K50)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N50" s="36" t="n"/>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M51" s="39">
         <f>IF(OR(B51="",L51="Feito",L51="Cancelado",L51="Sem prazo",L51="Depois"),0,IF(L51="Atrasada",2000,IF(L51="Hoje",1500,500))+F51*G51*100+IF(K51&lt;0,MIN(-K51,30),10-K51)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N51" s="36" t="n"/>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="M52" s="39">
         <f>IF(OR(B52="",L52="Feito",L52="Cancelado",L52="Sem prazo",L52="Depois"),0,IF(L52="Atrasada",2000,IF(L52="Hoje",1500,500))+F52*G52*100+IF(K52&lt;0,MIN(-K52,30),10-K52)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N52" s="36" t="n"/>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M53" s="39">
         <f>IF(OR(B53="",L53="Feito",L53="Cancelado",L53="Sem prazo",L53="Depois"),0,IF(L53="Atrasada",2000,IF(L53="Hoje",1500,500))+F53*G53*100+IF(K53&lt;0,MIN(-K53,30),10-K53)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N53" s="36" t="n"/>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M54" s="39">
         <f>IF(OR(B54="",L54="Feito",L54="Cancelado",L54="Sem prazo",L54="Depois"),0,IF(L54="Atrasada",2000,IF(L54="Hoje",1500,500))+F54*G54*100+IF(K54&lt;0,MIN(-K54,30),10-K54)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N54" s="36" t="n"/>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="M55" s="39">
         <f>IF(OR(B55="",L55="Feito",L55="Cancelado",L55="Sem prazo",L55="Depois"),0,IF(L55="Atrasada",2000,IF(L55="Hoje",1500,500))+F55*G55*100+IF(K55&lt;0,MIN(-K55,30),10-K55)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N55" s="36" t="n"/>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="M56" s="39">
         <f>IF(OR(B56="",L56="Feito",L56="Cancelado",L56="Sem prazo",L56="Depois"),0,IF(L56="Atrasada",2000,IF(L56="Hoje",1500,500))+F56*G56*100+IF(K56&lt;0,MIN(-K56,30),10-K56)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N56" s="36" t="n"/>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="M57" s="39">
         <f>IF(OR(B57="",L57="Feito",L57="Cancelado",L57="Sem prazo",L57="Depois"),0,IF(L57="Atrasada",2000,IF(L57="Hoje",1500,500))+F57*G57*100+IF(K57&lt;0,MIN(-K57,30),10-K57)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N57" s="36" t="n"/>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M58" s="39">
         <f>IF(OR(B58="",L58="Feito",L58="Cancelado",L58="Sem prazo",L58="Depois"),0,IF(L58="Atrasada",2000,IF(L58="Hoje",1500,500))+F58*G58*100+IF(K58&lt;0,MIN(-K58,30),10-K58)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N58" s="36" t="n"/>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="M59" s="39">
         <f>IF(OR(B59="",L59="Feito",L59="Cancelado",L59="Sem prazo",L59="Depois"),0,IF(L59="Atrasada",2000,IF(L59="Hoje",1500,500))+F59*G59*100+IF(K59&lt;0,MIN(-K59,30),10-K59)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N59" s="36" t="n"/>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="M60" s="39">
         <f>IF(OR(B60="",L60="Feito",L60="Cancelado",L60="Sem prazo",L60="Depois"),0,IF(L60="Atrasada",2000,IF(L60="Hoje",1500,500))+F60*G60*100+IF(K60&lt;0,MIN(-K60,30),10-K60)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N60" s="36" t="n"/>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="M61" s="39">
         <f>IF(OR(B61="",L61="Feito",L61="Cancelado",L61="Sem prazo",L61="Depois"),0,IF(L61="Atrasada",2000,IF(L61="Hoje",1500,500))+F61*G61*100+IF(K61&lt;0,MIN(-K61,30),10-K61)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N61" s="36" t="n"/>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="M62" s="39">
         <f>IF(OR(B62="",L62="Feito",L62="Cancelado",L62="Sem prazo",L62="Depois"),0,IF(L62="Atrasada",2000,IF(L62="Hoje",1500,500))+F62*G62*100+IF(K62&lt;0,MIN(-K62,30),10-K62)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N62" s="36" t="n"/>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="M63" s="39">
         <f>IF(OR(B63="",L63="Feito",L63="Cancelado",L63="Sem prazo",L63="Depois"),0,IF(L63="Atrasada",2000,IF(L63="Hoje",1500,500))+F63*G63*100+IF(K63&lt;0,MIN(-K63,30),10-K63)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N63" s="36" t="n"/>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="M64" s="39">
         <f>IF(OR(B64="",L64="Feito",L64="Cancelado",L64="Sem prazo",L64="Depois"),0,IF(L64="Atrasada",2000,IF(L64="Hoje",1500,500))+F64*G64*100+IF(K64&lt;0,MIN(-K64,30),10-K64)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N64" s="36" t="n"/>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="M65" s="39">
         <f>IF(OR(B65="",L65="Feito",L65="Cancelado",L65="Sem prazo",L65="Depois"),0,IF(L65="Atrasada",2000,IF(L65="Hoje",1500,500))+F65*G65*100+IF(K65&lt;0,MIN(-K65,30),10-K65)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N65" s="36" t="n"/>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="M66" s="39">
         <f>IF(OR(B66="",L66="Feito",L66="Cancelado",L66="Sem prazo",L66="Depois"),0,IF(L66="Atrasada",2000,IF(L66="Hoje",1500,500))+F66*G66*100+IF(K66&lt;0,MIN(-K66,30),10-K66)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N66" s="36" t="n"/>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="M67" s="39">
         <f>IF(OR(B67="",L67="Feito",L67="Cancelado",L67="Sem prazo",L67="Depois"),0,IF(L67="Atrasada",2000,IF(L67="Hoje",1500,500))+F67*G67*100+IF(K67&lt;0,MIN(-K67,30),10-K67)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N67" s="36" t="n"/>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="M68" s="39">
         <f>IF(OR(B68="",L68="Feito",L68="Cancelado",L68="Sem prazo",L68="Depois"),0,IF(L68="Atrasada",2000,IF(L68="Hoje",1500,500))+F68*G68*100+IF(K68&lt;0,MIN(-K68,30),10-K68)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N68" s="36" t="n"/>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M69" s="39">
         <f>IF(OR(B69="",L69="Feito",L69="Cancelado",L69="Sem prazo",L69="Depois"),0,IF(L69="Atrasada",2000,IF(L69="Hoje",1500,500))+F69*G69*100+IF(K69&lt;0,MIN(-K69,30),10-K69)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N69" s="36" t="n"/>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="M70" s="39">
         <f>IF(OR(B70="",L70="Feito",L70="Cancelado",L70="Sem prazo",L70="Depois"),0,IF(L70="Atrasada",2000,IF(L70="Hoje",1500,500))+F70*G70*100+IF(K70&lt;0,MIN(-K70,30),10-K70)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N70" s="36" t="n"/>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="M71" s="39">
         <f>IF(OR(B71="",L71="Feito",L71="Cancelado",L71="Sem prazo",L71="Depois"),0,IF(L71="Atrasada",2000,IF(L71="Hoje",1500,500))+F71*G71*100+IF(K71&lt;0,MIN(-K71,30),10-K71)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N71" s="36" t="n"/>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="M72" s="39">
         <f>IF(OR(B72="",L72="Feito",L72="Cancelado",L72="Sem prazo",L72="Depois"),0,IF(L72="Atrasada",2000,IF(L72="Hoje",1500,500))+F72*G72*100+IF(K72&lt;0,MIN(-K72,30),10-K72)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N72" s="36" t="n"/>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="M73" s="39">
         <f>IF(OR(B73="",L73="Feito",L73="Cancelado",L73="Sem prazo",L73="Depois"),0,IF(L73="Atrasada",2000,IF(L73="Hoje",1500,500))+F73*G73*100+IF(K73&lt;0,MIN(-K73,30),10-K73)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N73" s="36" t="n"/>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="M74" s="39">
         <f>IF(OR(B74="",L74="Feito",L74="Cancelado",L74="Sem prazo",L74="Depois"),0,IF(L74="Atrasada",2000,IF(L74="Hoje",1500,500))+F74*G74*100+IF(K74&lt;0,MIN(-K74,30),10-K74)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N74" s="36" t="n"/>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M75" s="39">
         <f>IF(OR(B75="",L75="Feito",L75="Cancelado",L75="Sem prazo",L75="Depois"),0,IF(L75="Atrasada",2000,IF(L75="Hoje",1500,500))+F75*G75*100+IF(K75&lt;0,MIN(-K75,30),10-K75)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N75" s="36" t="n"/>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M76" s="39">
         <f>IF(OR(B76="",L76="Feito",L76="Cancelado",L76="Sem prazo",L76="Depois"),0,IF(L76="Atrasada",2000,IF(L76="Hoje",1500,500))+F76*G76*100+IF(K76&lt;0,MIN(-K76,30),10-K76)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N76" s="36" t="n"/>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="M77" s="39">
         <f>IF(OR(B77="",L77="Feito",L77="Cancelado",L77="Sem prazo",L77="Depois"),0,IF(L77="Atrasada",2000,IF(L77="Hoje",1500,500))+F77*G77*100+IF(K77&lt;0,MIN(-K77,30),10-K77)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N77" s="36" t="n"/>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="M78" s="39">
         <f>IF(OR(B78="",L78="Feito",L78="Cancelado",L78="Sem prazo",L78="Depois"),0,IF(L78="Atrasada",2000,IF(L78="Hoje",1500,500))+F78*G78*100+IF(K78&lt;0,MIN(-K78,30),10-K78)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N78" s="36" t="n"/>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M79" s="39">
         <f>IF(OR(B79="",L79="Feito",L79="Cancelado",L79="Sem prazo",L79="Depois"),0,IF(L79="Atrasada",2000,IF(L79="Hoje",1500,500))+F79*G79*100+IF(K79&lt;0,MIN(-K79,30),10-K79)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N79" s="36" t="n"/>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="M80" s="39">
         <f>IF(OR(B80="",L80="Feito",L80="Cancelado",L80="Sem prazo",L80="Depois"),0,IF(L80="Atrasada",2000,IF(L80="Hoje",1500,500))+F80*G80*100+IF(K80&lt;0,MIN(-K80,30),10-K80)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N80" s="36" t="n"/>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="M81" s="39">
         <f>IF(OR(B81="",L81="Feito",L81="Cancelado",L81="Sem prazo",L81="Depois"),0,IF(L81="Atrasada",2000,IF(L81="Hoje",1500,500))+F81*G81*100+IF(K81&lt;0,MIN(-K81,30),10-K81)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N81" s="36" t="n"/>
     </row>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="M82" s="39">
         <f>IF(OR(B82="",L82="Feito",L82="Cancelado",L82="Sem prazo",L82="Depois"),0,IF(L82="Atrasada",2000,IF(L82="Hoje",1500,500))+F82*G82*100+IF(K82&lt;0,MIN(-K82,30),10-K82)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N82" s="36" t="n"/>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="M83" s="39">
         <f>IF(OR(B83="",L83="Feito",L83="Cancelado",L83="Sem prazo",L83="Depois"),0,IF(L83="Atrasada",2000,IF(L83="Hoje",1500,500))+F83*G83*100+IF(K83&lt;0,MIN(-K83,30),10-K83)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N83" s="36" t="n"/>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="M84" s="39">
         <f>IF(OR(B84="",L84="Feito",L84="Cancelado",L84="Sem prazo",L84="Depois"),0,IF(L84="Atrasada",2000,IF(L84="Hoje",1500,500))+F84*G84*100+IF(K84&lt;0,MIN(-K84,30),10-K84)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N84" s="36" t="n"/>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="M85" s="39">
         <f>IF(OR(B85="",L85="Feito",L85="Cancelado",L85="Sem prazo",L85="Depois"),0,IF(L85="Atrasada",2000,IF(L85="Hoje",1500,500))+F85*G85*100+IF(K85&lt;0,MIN(-K85,30),10-K85)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N85" s="36" t="n"/>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="M86" s="39">
         <f>IF(OR(B86="",L86="Feito",L86="Cancelado",L86="Sem prazo",L86="Depois"),0,IF(L86="Atrasada",2000,IF(L86="Hoje",1500,500))+F86*G86*100+IF(K86&lt;0,MIN(-K86,30),10-K86)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N86" s="36" t="n"/>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="M87" s="39">
         <f>IF(OR(B87="",L87="Feito",L87="Cancelado",L87="Sem prazo",L87="Depois"),0,IF(L87="Atrasada",2000,IF(L87="Hoje",1500,500))+F87*G87*100+IF(K87&lt;0,MIN(-K87,30),10-K87)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N87" s="36" t="n"/>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="M88" s="39">
         <f>IF(OR(B88="",L88="Feito",L88="Cancelado",L88="Sem prazo",L88="Depois"),0,IF(L88="Atrasada",2000,IF(L88="Hoje",1500,500))+F88*G88*100+IF(K88&lt;0,MIN(-K88,30),10-K88)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N88" s="36" t="n"/>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="M89" s="39">
         <f>IF(OR(B89="",L89="Feito",L89="Cancelado",L89="Sem prazo",L89="Depois"),0,IF(L89="Atrasada",2000,IF(L89="Hoje",1500,500))+F89*G89*100+IF(K89&lt;0,MIN(-K89,30),10-K89)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N89" s="36" t="n"/>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="M90" s="39">
         <f>IF(OR(B90="",L90="Feito",L90="Cancelado",L90="Sem prazo",L90="Depois"),0,IF(L90="Atrasada",2000,IF(L90="Hoje",1500,500))+F90*G90*100+IF(K90&lt;0,MIN(-K90,30),10-K90)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N90" s="36" t="n"/>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="M91" s="39">
         <f>IF(OR(B91="",L91="Feito",L91="Cancelado",L91="Sem prazo",L91="Depois"),0,IF(L91="Atrasada",2000,IF(L91="Hoje",1500,500))+F91*G91*100+IF(K91&lt;0,MIN(-K91,30),10-K91)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N91" s="36" t="n"/>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="M92" s="39">
         <f>IF(OR(B92="",L92="Feito",L92="Cancelado",L92="Sem prazo",L92="Depois"),0,IF(L92="Atrasada",2000,IF(L92="Hoje",1500,500))+F92*G92*100+IF(K92&lt;0,MIN(-K92,30),10-K92)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N92" s="36" t="n"/>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="M93" s="39">
         <f>IF(OR(B93="",L93="Feito",L93="Cancelado",L93="Sem prazo",L93="Depois"),0,IF(L93="Atrasada",2000,IF(L93="Hoje",1500,500))+F93*G93*100+IF(K93&lt;0,MIN(-K93,30),10-K93)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N93" s="36" t="n"/>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="M94" s="39">
         <f>IF(OR(B94="",L94="Feito",L94="Cancelado",L94="Sem prazo",L94="Depois"),0,IF(L94="Atrasada",2000,IF(L94="Hoje",1500,500))+F94*G94*100+IF(K94&lt;0,MIN(-K94,30),10-K94)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N94" s="36" t="n"/>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="M95" s="39">
         <f>IF(OR(B95="",L95="Feito",L95="Cancelado",L95="Sem prazo",L95="Depois"),0,IF(L95="Atrasada",2000,IF(L95="Hoje",1500,500))+F95*G95*100+IF(K95&lt;0,MIN(-K95,30),10-K95)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N95" s="36" t="n"/>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M96" s="39">
         <f>IF(OR(B96="",L96="Feito",L96="Cancelado",L96="Sem prazo",L96="Depois"),0,IF(L96="Atrasada",2000,IF(L96="Hoje",1500,500))+F96*G96*100+IF(K96&lt;0,MIN(-K96,30),10-K96)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N96" s="36" t="n"/>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="M97" s="39">
         <f>IF(OR(B97="",L97="Feito",L97="Cancelado",L97="Sem prazo",L97="Depois"),0,IF(L97="Atrasada",2000,IF(L97="Hoje",1500,500))+F97*G97*100+IF(K97&lt;0,MIN(-K97,30),10-K97)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N97" s="36" t="n"/>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="M98" s="39">
         <f>IF(OR(B98="",L98="Feito",L98="Cancelado",L98="Sem prazo",L98="Depois"),0,IF(L98="Atrasada",2000,IF(L98="Hoje",1500,500))+F98*G98*100+IF(K98&lt;0,MIN(-K98,30),10-K98)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N98" s="36" t="n"/>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="M99" s="39">
         <f>IF(OR(B99="",L99="Feito",L99="Cancelado",L99="Sem prazo",L99="Depois"),0,IF(L99="Atrasada",2000,IF(L99="Hoje",1500,500))+F99*G99*100+IF(K99&lt;0,MIN(-K99,30),10-K99)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N99" s="36" t="n"/>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="M100" s="39">
         <f>IF(OR(B100="",L100="Feito",L100="Cancelado",L100="Sem prazo",L100="Depois"),0,IF(L100="Atrasada",2000,IF(L100="Hoje",1500,500))+F100*G100*100+IF(K100&lt;0,MIN(-K100,30),10-K100)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N100" s="36" t="n"/>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="M101" s="39">
         <f>IF(OR(B101="",L101="Feito",L101="Cancelado",L101="Sem prazo",L101="Depois"),0,IF(L101="Atrasada",2000,IF(L101="Hoje",1500,500))+F101*G101*100+IF(K101&lt;0,MIN(-K101,30),10-K101)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N101" s="36" t="n"/>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="M102" s="39">
         <f>IF(OR(B102="",L102="Feito",L102="Cancelado",L102="Sem prazo",L102="Depois"),0,IF(L102="Atrasada",2000,IF(L102="Hoje",1500,500))+F102*G102*100+IF(K102&lt;0,MIN(-K102,30),10-K102)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N102" s="36" t="n"/>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="M103" s="39">
         <f>IF(OR(B103="",L103="Feito",L103="Cancelado",L103="Sem prazo",L103="Depois"),0,IF(L103="Atrasada",2000,IF(L103="Hoje",1500,500))+F103*G103*100+IF(K103&lt;0,MIN(-K103,30),10-K103)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N103" s="36" t="n"/>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="M104" s="39">
         <f>IF(OR(B104="",L104="Feito",L104="Cancelado",L104="Sem prazo",L104="Depois"),0,IF(L104="Atrasada",2000,IF(L104="Hoje",1500,500))+F104*G104*100+IF(K104&lt;0,MIN(-K104,30),10-K104)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N104" s="36" t="n"/>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M105" s="39">
         <f>IF(OR(B105="",L105="Feito",L105="Cancelado",L105="Sem prazo",L105="Depois"),0,IF(L105="Atrasada",2000,IF(L105="Hoje",1500,500))+F105*G105*100+IF(K105&lt;0,MIN(-K105,30),10-K105)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N105" s="36" t="n"/>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M106" s="39">
         <f>IF(OR(B106="",L106="Feito",L106="Cancelado",L106="Sem prazo",L106="Depois"),0,IF(L106="Atrasada",2000,IF(L106="Hoje",1500,500))+F106*G106*100+IF(K106&lt;0,MIN(-K106,30),10-K106)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N106" s="36" t="n"/>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="M107" s="39">
         <f>IF(OR(B107="",L107="Feito",L107="Cancelado",L107="Sem prazo",L107="Depois"),0,IF(L107="Atrasada",2000,IF(L107="Hoje",1500,500))+F107*G107*100+IF(K107&lt;0,MIN(-K107,30),10-K107)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N107" s="36" t="n"/>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="M108" s="39">
         <f>IF(OR(B108="",L108="Feito",L108="Cancelado",L108="Sem prazo",L108="Depois"),0,IF(L108="Atrasada",2000,IF(L108="Hoje",1500,500))+F108*G108*100+IF(K108&lt;0,MIN(-K108,30),10-K108)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N108" s="36" t="n"/>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="M109" s="39">
         <f>IF(OR(B109="",L109="Feito",L109="Cancelado",L109="Sem prazo",L109="Depois"),0,IF(L109="Atrasada",2000,IF(L109="Hoje",1500,500))+F109*G109*100+IF(K109&lt;0,MIN(-K109,30),10-K109)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N109" s="36" t="n"/>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="M110" s="39">
         <f>IF(OR(B110="",L110="Feito",L110="Cancelado",L110="Sem prazo",L110="Depois"),0,IF(L110="Atrasada",2000,IF(L110="Hoje",1500,500))+F110*G110*100+IF(K110&lt;0,MIN(-K110,30),10-K110)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N110" s="36" t="n"/>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="M111" s="39">
         <f>IF(OR(B111="",L111="Feito",L111="Cancelado",L111="Sem prazo",L111="Depois"),0,IF(L111="Atrasada",2000,IF(L111="Hoje",1500,500))+F111*G111*100+IF(K111&lt;0,MIN(-K111,30),10-K111)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N111" s="36" t="n"/>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="M112" s="39">
         <f>IF(OR(B112="",L112="Feito",L112="Cancelado",L112="Sem prazo",L112="Depois"),0,IF(L112="Atrasada",2000,IF(L112="Hoje",1500,500))+F112*G112*100+IF(K112&lt;0,MIN(-K112,30),10-K112)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N112" s="36" t="n"/>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="M113" s="39">
         <f>IF(OR(B113="",L113="Feito",L113="Cancelado",L113="Sem prazo",L113="Depois"),0,IF(L113="Atrasada",2000,IF(L113="Hoje",1500,500))+F113*G113*100+IF(K113&lt;0,MIN(-K113,30),10-K113)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N113" s="36" t="n"/>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="M114" s="39">
         <f>IF(OR(B114="",L114="Feito",L114="Cancelado",L114="Sem prazo",L114="Depois"),0,IF(L114="Atrasada",2000,IF(L114="Hoje",1500,500))+F114*G114*100+IF(K114&lt;0,MIN(-K114,30),10-K114)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N114" s="36" t="n"/>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M115" s="39">
         <f>IF(OR(B115="",L115="Feito",L115="Cancelado",L115="Sem prazo",L115="Depois"),0,IF(L115="Atrasada",2000,IF(L115="Hoje",1500,500))+F115*G115*100+IF(K115&lt;0,MIN(-K115,30),10-K115)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N115" s="36" t="n"/>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="M116" s="39">
         <f>IF(OR(B116="",L116="Feito",L116="Cancelado",L116="Sem prazo",L116="Depois"),0,IF(L116="Atrasada",2000,IF(L116="Hoje",1500,500))+F116*G116*100+IF(K116&lt;0,MIN(-K116,30),10-K116)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N116" s="36" t="n"/>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="M117" s="39">
         <f>IF(OR(B117="",L117="Feito",L117="Cancelado",L117="Sem prazo",L117="Depois"),0,IF(L117="Atrasada",2000,IF(L117="Hoje",1500,500))+F117*G117*100+IF(K117&lt;0,MIN(-K117,30),10-K117)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N117" s="36" t="n"/>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="M118" s="39">
         <f>IF(OR(B118="",L118="Feito",L118="Cancelado",L118="Sem prazo",L118="Depois"),0,IF(L118="Atrasada",2000,IF(L118="Hoje",1500,500))+F118*G118*100+IF(K118&lt;0,MIN(-K118,30),10-K118)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N118" s="36" t="n"/>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="M119" s="39">
         <f>IF(OR(B119="",L119="Feito",L119="Cancelado",L119="Sem prazo",L119="Depois"),0,IF(L119="Atrasada",2000,IF(L119="Hoje",1500,500))+F119*G119*100+IF(K119&lt;0,MIN(-K119,30),10-K119)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N119" s="36" t="n"/>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="M120" s="39">
         <f>IF(OR(B120="",L120="Feito",L120="Cancelado",L120="Sem prazo",L120="Depois"),0,IF(L120="Atrasada",2000,IF(L120="Hoje",1500,500))+F120*G120*100+IF(K120&lt;0,MIN(-K120,30),10-K120)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N120" s="36" t="n"/>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M121" s="39">
         <f>IF(OR(B121="",L121="Feito",L121="Cancelado",L121="Sem prazo",L121="Depois"),0,IF(L121="Atrasada",2000,IF(L121="Hoje",1500,500))+F121*G121*100+IF(K121&lt;0,MIN(-K121,30),10-K121)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N121" s="36" t="n"/>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="M122" s="39">
         <f>IF(OR(B122="",L122="Feito",L122="Cancelado",L122="Sem prazo",L122="Depois"),0,IF(L122="Atrasada",2000,IF(L122="Hoje",1500,500))+F122*G122*100+IF(K122&lt;0,MIN(-K122,30),10-K122)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N122" s="36" t="n"/>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="M123" s="39">
         <f>IF(OR(B123="",L123="Feito",L123="Cancelado",L123="Sem prazo",L123="Depois"),0,IF(L123="Atrasada",2000,IF(L123="Hoje",1500,500))+F123*G123*100+IF(K123&lt;0,MIN(-K123,30),10-K123)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N123" s="36" t="n"/>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="M124" s="39">
         <f>IF(OR(B124="",L124="Feito",L124="Cancelado",L124="Sem prazo",L124="Depois"),0,IF(L124="Atrasada",2000,IF(L124="Hoje",1500,500))+F124*G124*100+IF(K124&lt;0,MIN(-K124,30),10-K124)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N124" s="36" t="n"/>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="M125" s="39">
         <f>IF(OR(B125="",L125="Feito",L125="Cancelado",L125="Sem prazo",L125="Depois"),0,IF(L125="Atrasada",2000,IF(L125="Hoje",1500,500))+F125*G125*100+IF(K125&lt;0,MIN(-K125,30),10-K125)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N125" s="36" t="n"/>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="M126" s="39">
         <f>IF(OR(B126="",L126="Feito",L126="Cancelado",L126="Sem prazo",L126="Depois"),0,IF(L126="Atrasada",2000,IF(L126="Hoje",1500,500))+F126*G126*100+IF(K126&lt;0,MIN(-K126,30),10-K126)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N126" s="36" t="n"/>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="M127" s="39">
         <f>IF(OR(B127="",L127="Feito",L127="Cancelado",L127="Sem prazo",L127="Depois"),0,IF(L127="Atrasada",2000,IF(L127="Hoje",1500,500))+F127*G127*100+IF(K127&lt;0,MIN(-K127,30),10-K127)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N127" s="36" t="n"/>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="M128" s="39">
         <f>IF(OR(B128="",L128="Feito",L128="Cancelado",L128="Sem prazo",L128="Depois"),0,IF(L128="Atrasada",2000,IF(L128="Hoje",1500,500))+F128*G128*100+IF(K128&lt;0,MIN(-K128,30),10-K128)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N128" s="36" t="n"/>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="M129" s="39">
         <f>IF(OR(B129="",L129="Feito",L129="Cancelado",L129="Sem prazo",L129="Depois"),0,IF(L129="Atrasada",2000,IF(L129="Hoje",1500,500))+F129*G129*100+IF(K129&lt;0,MIN(-K129,30),10-K129)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N129" s="36" t="n"/>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="M130" s="39">
         <f>IF(OR(B130="",L130="Feito",L130="Cancelado",L130="Sem prazo",L130="Depois"),0,IF(L130="Atrasada",2000,IF(L130="Hoje",1500,500))+F130*G130*100+IF(K130&lt;0,MIN(-K130,30),10-K130)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N130" s="36" t="n"/>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="M131" s="39">
         <f>IF(OR(B131="",L131="Feito",L131="Cancelado",L131="Sem prazo",L131="Depois"),0,IF(L131="Atrasada",2000,IF(L131="Hoje",1500,500))+F131*G131*100+IF(K131&lt;0,MIN(-K131,30),10-K131)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N131" s="36" t="n"/>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="M132" s="39">
         <f>IF(OR(B132="",L132="Feito",L132="Cancelado",L132="Sem prazo",L132="Depois"),0,IF(L132="Atrasada",2000,IF(L132="Hoje",1500,500))+F132*G132*100+IF(K132&lt;0,MIN(-K132,30),10-K132)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N132" s="36" t="n"/>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="M133" s="39">
         <f>IF(OR(B133="",L133="Feito",L133="Cancelado",L133="Sem prazo",L133="Depois"),0,IF(L133="Atrasada",2000,IF(L133="Hoje",1500,500))+F133*G133*100+IF(K133&lt;0,MIN(-K133,30),10-K133)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N133" s="36" t="n"/>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="M134" s="39">
         <f>IF(OR(B134="",L134="Feito",L134="Cancelado",L134="Sem prazo",L134="Depois"),0,IF(L134="Atrasada",2000,IF(L134="Hoje",1500,500))+F134*G134*100+IF(K134&lt;0,MIN(-K134,30),10-K134)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N134" s="36" t="n"/>
     </row>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="M135" s="39">
         <f>IF(OR(B135="",L135="Feito",L135="Cancelado",L135="Sem prazo",L135="Depois"),0,IF(L135="Atrasada",2000,IF(L135="Hoje",1500,500))+F135*G135*100+IF(K135&lt;0,MIN(-K135,30),10-K135)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N135" s="36" t="n"/>
     </row>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="M136" s="39">
         <f>IF(OR(B136="",L136="Feito",L136="Cancelado",L136="Sem prazo",L136="Depois"),0,IF(L136="Atrasada",2000,IF(L136="Hoje",1500,500))+F136*G136*100+IF(K136&lt;0,MIN(-K136,30),10-K136)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N136" s="36" t="n"/>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="M137" s="39">
         <f>IF(OR(B137="",L137="Feito",L137="Cancelado",L137="Sem prazo",L137="Depois"),0,IF(L137="Atrasada",2000,IF(L137="Hoje",1500,500))+F137*G137*100+IF(K137&lt;0,MIN(-K137,30),10-K137)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N137" s="36" t="n"/>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M138" s="39">
         <f>IF(OR(B138="",L138="Feito",L138="Cancelado",L138="Sem prazo",L138="Depois"),0,IF(L138="Atrasada",2000,IF(L138="Hoje",1500,500))+F138*G138*100+IF(K138&lt;0,MIN(-K138,30),10-K138)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N138" s="36" t="n"/>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="M139" s="39">
         <f>IF(OR(B139="",L139="Feito",L139="Cancelado",L139="Sem prazo",L139="Depois"),0,IF(L139="Atrasada",2000,IF(L139="Hoje",1500,500))+F139*G139*100+IF(K139&lt;0,MIN(-K139,30),10-K139)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N139" s="36" t="n"/>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="M140" s="39">
         <f>IF(OR(B140="",L140="Feito",L140="Cancelado",L140="Sem prazo",L140="Depois"),0,IF(L140="Atrasada",2000,IF(L140="Hoje",1500,500))+F140*G140*100+IF(K140&lt;0,MIN(-K140,30),10-K140)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N140" s="36" t="n"/>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M141" s="39">
         <f>IF(OR(B141="",L141="Feito",L141="Cancelado",L141="Sem prazo",L141="Depois"),0,IF(L141="Atrasada",2000,IF(L141="Hoje",1500,500))+F141*G141*100+IF(K141&lt;0,MIN(-K141,30),10-K141)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N141" s="36" t="n"/>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M142" s="39">
         <f>IF(OR(B142="",L142="Feito",L142="Cancelado",L142="Sem prazo",L142="Depois"),0,IF(L142="Atrasada",2000,IF(L142="Hoje",1500,500))+F142*G142*100+IF(K142&lt;0,MIN(-K142,30),10-K142)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N142" s="36" t="n"/>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M143" s="39">
         <f>IF(OR(B143="",L143="Feito",L143="Cancelado",L143="Sem prazo",L143="Depois"),0,IF(L143="Atrasada",2000,IF(L143="Hoje",1500,500))+F143*G143*100+IF(K143&lt;0,MIN(-K143,30),10-K143)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N143" s="36" t="n"/>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="M144" s="39">
         <f>IF(OR(B144="",L144="Feito",L144="Cancelado",L144="Sem prazo",L144="Depois"),0,IF(L144="Atrasada",2000,IF(L144="Hoje",1500,500))+F144*G144*100+IF(K144&lt;0,MIN(-K144,30),10-K144)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N144" s="36" t="n"/>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="M145" s="39">
         <f>IF(OR(B145="",L145="Feito",L145="Cancelado",L145="Sem prazo",L145="Depois"),0,IF(L145="Atrasada",2000,IF(L145="Hoje",1500,500))+F145*G145*100+IF(K145&lt;0,MIN(-K145,30),10-K145)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N145" s="36" t="n"/>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="M146" s="39">
         <f>IF(OR(B146="",L146="Feito",L146="Cancelado",L146="Sem prazo",L146="Depois"),0,IF(L146="Atrasada",2000,IF(L146="Hoje",1500,500))+F146*G146*100+IF(K146&lt;0,MIN(-K146,30),10-K146)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N146" s="36" t="n"/>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="M147" s="39">
         <f>IF(OR(B147="",L147="Feito",L147="Cancelado",L147="Sem prazo",L147="Depois"),0,IF(L147="Atrasada",2000,IF(L147="Hoje",1500,500))+F147*G147*100+IF(K147&lt;0,MIN(-K147,30),10-K147)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N147" s="36" t="n"/>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="M148" s="39">
         <f>IF(OR(B148="",L148="Feito",L148="Cancelado",L148="Sem prazo",L148="Depois"),0,IF(L148="Atrasada",2000,IF(L148="Hoje",1500,500))+F148*G148*100+IF(K148&lt;0,MIN(-K148,30),10-K148)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N148" s="36" t="n"/>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="M149" s="39">
         <f>IF(OR(B149="",L149="Feito",L149="Cancelado",L149="Sem prazo",L149="Depois"),0,IF(L149="Atrasada",2000,IF(L149="Hoje",1500,500))+F149*G149*100+IF(K149&lt;0,MIN(-K149,30),10-K149)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N149" s="36" t="n"/>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="M150" s="39">
         <f>IF(OR(B150="",L150="Feito",L150="Cancelado",L150="Sem prazo",L150="Depois"),0,IF(L150="Atrasada",2000,IF(L150="Hoje",1500,500))+F150*G150*100+IF(K150&lt;0,MIN(-K150,30),10-K150)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N150" s="36" t="n"/>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="M151" s="39">
         <f>IF(OR(B151="",L151="Feito",L151="Cancelado",L151="Sem prazo",L151="Depois"),0,IF(L151="Atrasada",2000,IF(L151="Hoje",1500,500))+F151*G151*100+IF(K151&lt;0,MIN(-K151,30),10-K151)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N151" s="36" t="n"/>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="M152" s="39">
         <f>IF(OR(B152="",L152="Feito",L152="Cancelado",L152="Sem prazo",L152="Depois"),0,IF(L152="Atrasada",2000,IF(L152="Hoje",1500,500))+F152*G152*100+IF(K152&lt;0,MIN(-K152,30),10-K152)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N152" s="36" t="n"/>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="M153" s="39">
         <f>IF(OR(B153="",L153="Feito",L153="Cancelado",L153="Sem prazo",L153="Depois"),0,IF(L153="Atrasada",2000,IF(L153="Hoje",1500,500))+F153*G153*100+IF(K153&lt;0,MIN(-K153,30),10-K153)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N153" s="36" t="n"/>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="M154" s="39">
         <f>IF(OR(B154="",L154="Feito",L154="Cancelado",L154="Sem prazo",L154="Depois"),0,IF(L154="Atrasada",2000,IF(L154="Hoje",1500,500))+F154*G154*100+IF(K154&lt;0,MIN(-K154,30),10-K154)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N154" s="36" t="n"/>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="M155" s="39">
         <f>IF(OR(B155="",L155="Feito",L155="Cancelado",L155="Sem prazo",L155="Depois"),0,IF(L155="Atrasada",2000,IF(L155="Hoje",1500,500))+F155*G155*100+IF(K155&lt;0,MIN(-K155,30),10-K155)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N155" s="36" t="n"/>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="M156" s="39">
         <f>IF(OR(B156="",L156="Feito",L156="Cancelado",L156="Sem prazo",L156="Depois"),0,IF(L156="Atrasada",2000,IF(L156="Hoje",1500,500))+F156*G156*100+IF(K156&lt;0,MIN(-K156,30),10-K156)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N156" s="36" t="n"/>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M157" s="39">
         <f>IF(OR(B157="",L157="Feito",L157="Cancelado",L157="Sem prazo",L157="Depois"),0,IF(L157="Atrasada",2000,IF(L157="Hoje",1500,500))+F157*G157*100+IF(K157&lt;0,MIN(-K157,30),10-K157)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N157" s="36" t="n"/>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="M158" s="39">
         <f>IF(OR(B158="",L158="Feito",L158="Cancelado",L158="Sem prazo",L158="Depois"),0,IF(L158="Atrasada",2000,IF(L158="Hoje",1500,500))+F158*G158*100+IF(K158&lt;0,MIN(-K158,30),10-K158)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N158" s="36" t="n"/>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="M159" s="39">
         <f>IF(OR(B159="",L159="Feito",L159="Cancelado",L159="Sem prazo",L159="Depois"),0,IF(L159="Atrasada",2000,IF(L159="Hoje",1500,500))+F159*G159*100+IF(K159&lt;0,MIN(-K159,30),10-K159)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N159" s="36" t="n"/>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M160" s="39">
         <f>IF(OR(B160="",L160="Feito",L160="Cancelado",L160="Sem prazo",L160="Depois"),0,IF(L160="Atrasada",2000,IF(L160="Hoje",1500,500))+F160*G160*100+IF(K160&lt;0,MIN(-K160,30),10-K160)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N160" s="36" t="n"/>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="M161" s="39">
         <f>IF(OR(B161="",L161="Feito",L161="Cancelado",L161="Sem prazo",L161="Depois"),0,IF(L161="Atrasada",2000,IF(L161="Hoje",1500,500))+F161*G161*100+IF(K161&lt;0,MIN(-K161,30),10-K161)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N161" s="36" t="n"/>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="M162" s="39">
         <f>IF(OR(B162="",L162="Feito",L162="Cancelado",L162="Sem prazo",L162="Depois"),0,IF(L162="Atrasada",2000,IF(L162="Hoje",1500,500))+F162*G162*100+IF(K162&lt;0,MIN(-K162,30),10-K162)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N162" s="36" t="n"/>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="M163" s="39">
         <f>IF(OR(B163="",L163="Feito",L163="Cancelado",L163="Sem prazo",L163="Depois"),0,IF(L163="Atrasada",2000,IF(L163="Hoje",1500,500))+F163*G163*100+IF(K163&lt;0,MIN(-K163,30),10-K163)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N163" s="36" t="n"/>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M164" s="39">
         <f>IF(OR(B164="",L164="Feito",L164="Cancelado",L164="Sem prazo",L164="Depois"),0,IF(L164="Atrasada",2000,IF(L164="Hoje",1500,500))+F164*G164*100+IF(K164&lt;0,MIN(-K164,30),10-K164)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N164" s="36" t="n"/>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="M165" s="39">
         <f>IF(OR(B165="",L165="Feito",L165="Cancelado",L165="Sem prazo",L165="Depois"),0,IF(L165="Atrasada",2000,IF(L165="Hoje",1500,500))+F165*G165*100+IF(K165&lt;0,MIN(-K165,30),10-K165)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N165" s="36" t="n"/>
     </row>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M166" s="39">
         <f>IF(OR(B166="",L166="Feito",L166="Cancelado",L166="Sem prazo",L166="Depois"),0,IF(L166="Atrasada",2000,IF(L166="Hoje",1500,500))+F166*G166*100+IF(K166&lt;0,MIN(-K166,30),10-K166)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N166" s="36" t="n"/>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="M167" s="39">
         <f>IF(OR(B167="",L167="Feito",L167="Cancelado",L167="Sem prazo",L167="Depois"),0,IF(L167="Atrasada",2000,IF(L167="Hoje",1500,500))+F167*G167*100+IF(K167&lt;0,MIN(-K167,30),10-K167)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N167" s="36" t="n"/>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="M168" s="39">
         <f>IF(OR(B168="",L168="Feito",L168="Cancelado",L168="Sem prazo",L168="Depois"),0,IF(L168="Atrasada",2000,IF(L168="Hoje",1500,500))+F168*G168*100+IF(K168&lt;0,MIN(-K168,30),10-K168)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N168" s="36" t="n"/>
     </row>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="M169" s="39">
         <f>IF(OR(B169="",L169="Feito",L169="Cancelado",L169="Sem prazo",L169="Depois"),0,IF(L169="Atrasada",2000,IF(L169="Hoje",1500,500))+F169*G169*100+IF(K169&lt;0,MIN(-K169,30),10-K169)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N169" s="36" t="n"/>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="M170" s="39">
         <f>IF(OR(B170="",L170="Feito",L170="Cancelado",L170="Sem prazo",L170="Depois"),0,IF(L170="Atrasada",2000,IF(L170="Hoje",1500,500))+F170*G170*100+IF(K170&lt;0,MIN(-K170,30),10-K170)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N170" s="36" t="n"/>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="M171" s="39">
         <f>IF(OR(B171="",L171="Feito",L171="Cancelado",L171="Sem prazo",L171="Depois"),0,IF(L171="Atrasada",2000,IF(L171="Hoje",1500,500))+F171*G171*100+IF(K171&lt;0,MIN(-K171,30),10-K171)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N171" s="36" t="n"/>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="M172" s="39">
         <f>IF(OR(B172="",L172="Feito",L172="Cancelado",L172="Sem prazo",L172="Depois"),0,IF(L172="Atrasada",2000,IF(L172="Hoje",1500,500))+F172*G172*100+IF(K172&lt;0,MIN(-K172,30),10-K172)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N172" s="36" t="n"/>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="M173" s="39">
         <f>IF(OR(B173="",L173="Feito",L173="Cancelado",L173="Sem prazo",L173="Depois"),0,IF(L173="Atrasada",2000,IF(L173="Hoje",1500,500))+F173*G173*100+IF(K173&lt;0,MIN(-K173,30),10-K173)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N173" s="36" t="n"/>
     </row>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="M174" s="39">
         <f>IF(OR(B174="",L174="Feito",L174="Cancelado",L174="Sem prazo",L174="Depois"),0,IF(L174="Atrasada",2000,IF(L174="Hoje",1500,500))+F174*G174*100+IF(K174&lt;0,MIN(-K174,30),10-K174)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N174" s="36" t="n"/>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M175" s="39">
         <f>IF(OR(B175="",L175="Feito",L175="Cancelado",L175="Sem prazo",L175="Depois"),0,IF(L175="Atrasada",2000,IF(L175="Hoje",1500,500))+F175*G175*100+IF(K175&lt;0,MIN(-K175,30),10-K175)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N175" s="36" t="n"/>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="M176" s="39">
         <f>IF(OR(B176="",L176="Feito",L176="Cancelado",L176="Sem prazo",L176="Depois"),0,IF(L176="Atrasada",2000,IF(L176="Hoje",1500,500))+F176*G176*100+IF(K176&lt;0,MIN(-K176,30),10-K176)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N176" s="36" t="n"/>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="M177" s="39">
         <f>IF(OR(B177="",L177="Feito",L177="Cancelado",L177="Sem prazo",L177="Depois"),0,IF(L177="Atrasada",2000,IF(L177="Hoje",1500,500))+F177*G177*100+IF(K177&lt;0,MIN(-K177,30),10-K177)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N177" s="36" t="n"/>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="M178" s="39">
         <f>IF(OR(B178="",L178="Feito",L178="Cancelado",L178="Sem prazo",L178="Depois"),0,IF(L178="Atrasada",2000,IF(L178="Hoje",1500,500))+F178*G178*100+IF(K178&lt;0,MIN(-K178,30),10-K178)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N178" s="36" t="n"/>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="M179" s="39">
         <f>IF(OR(B179="",L179="Feito",L179="Cancelado",L179="Sem prazo",L179="Depois"),0,IF(L179="Atrasada",2000,IF(L179="Hoje",1500,500))+F179*G179*100+IF(K179&lt;0,MIN(-K179,30),10-K179)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N179" s="36" t="n"/>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="M180" s="39">
         <f>IF(OR(B180="",L180="Feito",L180="Cancelado",L180="Sem prazo",L180="Depois"),0,IF(L180="Atrasada",2000,IF(L180="Hoje",1500,500))+F180*G180*100+IF(K180&lt;0,MIN(-K180,30),10-K180)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N180" s="36" t="n"/>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M181" s="39">
         <f>IF(OR(B181="",L181="Feito",L181="Cancelado",L181="Sem prazo",L181="Depois"),0,IF(L181="Atrasada",2000,IF(L181="Hoje",1500,500))+F181*G181*100+IF(K181&lt;0,MIN(-K181,30),10-K181)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N181" s="36" t="n"/>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M182" s="39">
         <f>IF(OR(B182="",L182="Feito",L182="Cancelado",L182="Sem prazo",L182="Depois"),0,IF(L182="Atrasada",2000,IF(L182="Hoje",1500,500))+F182*G182*100+IF(K182&lt;0,MIN(-K182,30),10-K182)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N182" s="36" t="n"/>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="M183" s="39">
         <f>IF(OR(B183="",L183="Feito",L183="Cancelado",L183="Sem prazo",L183="Depois"),0,IF(L183="Atrasada",2000,IF(L183="Hoje",1500,500))+F183*G183*100+IF(K183&lt;0,MIN(-K183,30),10-K183)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N183" s="36" t="n"/>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="M184" s="39">
         <f>IF(OR(B184="",L184="Feito",L184="Cancelado",L184="Sem prazo",L184="Depois"),0,IF(L184="Atrasada",2000,IF(L184="Hoje",1500,500))+F184*G184*100+IF(K184&lt;0,MIN(-K184,30),10-K184)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N184" s="36" t="n"/>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="M185" s="39">
         <f>IF(OR(B185="",L185="Feito",L185="Cancelado",L185="Sem prazo",L185="Depois"),0,IF(L185="Atrasada",2000,IF(L185="Hoje",1500,500))+F185*G185*100+IF(K185&lt;0,MIN(-K185,30),10-K185)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N185" s="36" t="n"/>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="M186" s="39">
         <f>IF(OR(B186="",L186="Feito",L186="Cancelado",L186="Sem prazo",L186="Depois"),0,IF(L186="Atrasada",2000,IF(L186="Hoje",1500,500))+F186*G186*100+IF(K186&lt;0,MIN(-K186,30),10-K186)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N186" s="36" t="n"/>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="M187" s="39">
         <f>IF(OR(B187="",L187="Feito",L187="Cancelado",L187="Sem prazo",L187="Depois"),0,IF(L187="Atrasada",2000,IF(L187="Hoje",1500,500))+F187*G187*100+IF(K187&lt;0,MIN(-K187,30),10-K187)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N187" s="36" t="n"/>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="M188" s="39">
         <f>IF(OR(B188="",L188="Feito",L188="Cancelado",L188="Sem prazo",L188="Depois"),0,IF(L188="Atrasada",2000,IF(L188="Hoje",1500,500))+F188*G188*100+IF(K188&lt;0,MIN(-K188,30),10-K188)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N188" s="36" t="n"/>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="M189" s="39">
         <f>IF(OR(B189="",L189="Feito",L189="Cancelado",L189="Sem prazo",L189="Depois"),0,IF(L189="Atrasada",2000,IF(L189="Hoje",1500,500))+F189*G189*100+IF(K189&lt;0,MIN(-K189,30),10-K189)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N189" s="36" t="n"/>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="M190" s="39">
         <f>IF(OR(B190="",L190="Feito",L190="Cancelado",L190="Sem prazo",L190="Depois"),0,IF(L190="Atrasada",2000,IF(L190="Hoje",1500,500))+F190*G190*100+IF(K190&lt;0,MIN(-K190,30),10-K190)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N190" s="36" t="n"/>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="M191" s="39">
         <f>IF(OR(B191="",L191="Feito",L191="Cancelado",L191="Sem prazo",L191="Depois"),0,IF(L191="Atrasada",2000,IF(L191="Hoje",1500,500))+F191*G191*100+IF(K191&lt;0,MIN(-K191,30),10-K191)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N191" s="36" t="n"/>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="M192" s="39">
         <f>IF(OR(B192="",L192="Feito",L192="Cancelado",L192="Sem prazo",L192="Depois"),0,IF(L192="Atrasada",2000,IF(L192="Hoje",1500,500))+F192*G192*100+IF(K192&lt;0,MIN(-K192,30),10-K192)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N192" s="36" t="n"/>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="M193" s="39">
         <f>IF(OR(B193="",L193="Feito",L193="Cancelado",L193="Sem prazo",L193="Depois"),0,IF(L193="Atrasada",2000,IF(L193="Hoje",1500,500))+F193*G193*100+IF(K193&lt;0,MIN(-K193,30),10-K193)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N193" s="36" t="n"/>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="M194" s="39">
         <f>IF(OR(B194="",L194="Feito",L194="Cancelado",L194="Sem prazo",L194="Depois"),0,IF(L194="Atrasada",2000,IF(L194="Hoje",1500,500))+F194*G194*100+IF(K194&lt;0,MIN(-K194,30),10-K194)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N194" s="36" t="n"/>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="M195" s="39">
         <f>IF(OR(B195="",L195="Feito",L195="Cancelado",L195="Sem prazo",L195="Depois"),0,IF(L195="Atrasada",2000,IF(L195="Hoje",1500,500))+F195*G195*100+IF(K195&lt;0,MIN(-K195,30),10-K195)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N195" s="36" t="n"/>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="M196" s="39">
         <f>IF(OR(B196="",L196="Feito",L196="Cancelado",L196="Sem prazo",L196="Depois"),0,IF(L196="Atrasada",2000,IF(L196="Hoje",1500,500))+F196*G196*100+IF(K196&lt;0,MIN(-K196,30),10-K196)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N196" s="36" t="n"/>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="M197" s="39">
         <f>IF(OR(B197="",L197="Feito",L197="Cancelado",L197="Sem prazo",L197="Depois"),0,IF(L197="Atrasada",2000,IF(L197="Hoje",1500,500))+F197*G197*100+IF(K197&lt;0,MIN(-K197,30),10-K197)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N197" s="36" t="n"/>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="M198" s="39">
         <f>IF(OR(B198="",L198="Feito",L198="Cancelado",L198="Sem prazo",L198="Depois"),0,IF(L198="Atrasada",2000,IF(L198="Hoje",1500,500))+F198*G198*100+IF(K198&lt;0,MIN(-K198,30),10-K198)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N198" s="36" t="n"/>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="M199" s="39">
         <f>IF(OR(B199="",L199="Feito",L199="Cancelado",L199="Sem prazo",L199="Depois"),0,IF(L199="Atrasada",2000,IF(L199="Hoje",1500,500))+F199*G199*100+IF(K199&lt;0,MIN(-K199,30),10-K199)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N199" s="36" t="n"/>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="M200" s="39">
         <f>IF(OR(B200="",L200="Feito",L200="Cancelado",L200="Sem prazo",L200="Depois"),0,IF(L200="Atrasada",2000,IF(L200="Hoje",1500,500))+F200*G200*100+IF(K200&lt;0,MIN(-K200,30),10-K200)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N200" s="36" t="n"/>
     </row>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="M201" s="39">
         <f>IF(OR(B201="",L201="Feito",L201="Cancelado",L201="Sem prazo",L201="Depois"),0,IF(L201="Atrasada",2000,IF(L201="Hoje",1500,500))+F201*G201*100+IF(K201&lt;0,MIN(-K201,30),10-K201)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N201" s="36" t="n"/>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="M202" s="39">
         <f>IF(OR(B202="",L202="Feito",L202="Cancelado",L202="Sem prazo",L202="Depois"),0,IF(L202="Atrasada",2000,IF(L202="Hoje",1500,500))+F202*G202*100+IF(K202&lt;0,MIN(-K202,30),10-K202)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N202" s="36" t="n"/>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="M203" s="39">
         <f>IF(OR(B203="",L203="Feito",L203="Cancelado",L203="Sem prazo",L203="Depois"),0,IF(L203="Atrasada",2000,IF(L203="Hoje",1500,500))+F203*G203*100+IF(K203&lt;0,MIN(-K203,30),10-K203)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N203" s="36" t="n"/>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M204" s="39">
         <f>IF(OR(B204="",L204="Feito",L204="Cancelado",L204="Sem prazo",L204="Depois"),0,IF(L204="Atrasada",2000,IF(L204="Hoje",1500,500))+F204*G204*100+IF(K204&lt;0,MIN(-K204,30),10-K204)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N204" s="36" t="n"/>
     </row>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M205" s="39">
         <f>IF(OR(B205="",L205="Feito",L205="Cancelado",L205="Sem prazo",L205="Depois"),0,IF(L205="Atrasada",2000,IF(L205="Hoje",1500,500))+F205*G205*100+IF(K205&lt;0,MIN(-K205,30),10-K205)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N205" s="36" t="n"/>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M206" s="39">
         <f>IF(OR(B206="",L206="Feito",L206="Cancelado",L206="Sem prazo",L206="Depois"),0,IF(L206="Atrasada",2000,IF(L206="Hoje",1500,500))+F206*G206*100+IF(K206&lt;0,MIN(-K206,30),10-K206)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N206" s="36" t="n"/>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="M207" s="39">
         <f>IF(OR(B207="",L207="Feito",L207="Cancelado",L207="Sem prazo",L207="Depois"),0,IF(L207="Atrasada",2000,IF(L207="Hoje",1500,500))+F207*G207*100+IF(K207&lt;0,MIN(-K207,30),10-K207)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N207" s="36" t="n"/>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="M208" s="39">
         <f>IF(OR(B208="",L208="Feito",L208="Cancelado",L208="Sem prazo",L208="Depois"),0,IF(L208="Atrasada",2000,IF(L208="Hoje",1500,500))+F208*G208*100+IF(K208&lt;0,MIN(-K208,30),10-K208)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N208" s="36" t="n"/>
     </row>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="M209" s="39">
         <f>IF(OR(B209="",L209="Feito",L209="Cancelado",L209="Sem prazo",L209="Depois"),0,IF(L209="Atrasada",2000,IF(L209="Hoje",1500,500))+F209*G209*100+IF(K209&lt;0,MIN(-K209,30),10-K209)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N209" s="36" t="n"/>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M210" s="39">
         <f>IF(OR(B210="",L210="Feito",L210="Cancelado",L210="Sem prazo",L210="Depois"),0,IF(L210="Atrasada",2000,IF(L210="Hoje",1500,500))+F210*G210*100+IF(K210&lt;0,MIN(-K210,30),10-K210)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N210" s="36" t="n"/>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="M211" s="39">
         <f>IF(OR(B211="",L211="Feito",L211="Cancelado",L211="Sem prazo",L211="Depois"),0,IF(L211="Atrasada",2000,IF(L211="Hoje",1500,500))+F211*G211*100+IF(K211&lt;0,MIN(-K211,30),10-K211)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N211" s="36" t="n"/>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="M212" s="39">
         <f>IF(OR(B212="",L212="Feito",L212="Cancelado",L212="Sem prazo",L212="Depois"),0,IF(L212="Atrasada",2000,IF(L212="Hoje",1500,500))+F212*G212*100+IF(K212&lt;0,MIN(-K212,30),10-K212)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N212" s="36" t="n"/>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="M213" s="39">
         <f>IF(OR(B213="",L213="Feito",L213="Cancelado",L213="Sem prazo",L213="Depois"),0,IF(L213="Atrasada",2000,IF(L213="Hoje",1500,500))+F213*G213*100+IF(K213&lt;0,MIN(-K213,30),10-K213)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N213" s="36" t="n"/>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="M214" s="39">
         <f>IF(OR(B214="",L214="Feito",L214="Cancelado",L214="Sem prazo",L214="Depois"),0,IF(L214="Atrasada",2000,IF(L214="Hoje",1500,500))+F214*G214*100+IF(K214&lt;0,MIN(-K214,30),10-K214)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N214" s="36" t="n"/>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="M215" s="39">
         <f>IF(OR(B215="",L215="Feito",L215="Cancelado",L215="Sem prazo",L215="Depois"),0,IF(L215="Atrasada",2000,IF(L215="Hoje",1500,500))+F215*G215*100+IF(K215&lt;0,MIN(-K215,30),10-K215)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N215" s="36" t="n"/>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M216" s="39">
         <f>IF(OR(B216="",L216="Feito",L216="Cancelado",L216="Sem prazo",L216="Depois"),0,IF(L216="Atrasada",2000,IF(L216="Hoje",1500,500))+F216*G216*100+IF(K216&lt;0,MIN(-K216,30),10-K216)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N216" s="36" t="n"/>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="M217" s="39">
         <f>IF(OR(B217="",L217="Feito",L217="Cancelado",L217="Sem prazo",L217="Depois"),0,IF(L217="Atrasada",2000,IF(L217="Hoje",1500,500))+F217*G217*100+IF(K217&lt;0,MIN(-K217,30),10-K217)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N217" s="36" t="n"/>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="M218" s="39">
         <f>IF(OR(B218="",L218="Feito",L218="Cancelado",L218="Sem prazo",L218="Depois"),0,IF(L218="Atrasada",2000,IF(L218="Hoje",1500,500))+F218*G218*100+IF(K218&lt;0,MIN(-K218,30),10-K218)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N218" s="36" t="n"/>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="M219" s="39">
         <f>IF(OR(B219="",L219="Feito",L219="Cancelado",L219="Sem prazo",L219="Depois"),0,IF(L219="Atrasada",2000,IF(L219="Hoje",1500,500))+F219*G219*100+IF(K219&lt;0,MIN(-K219,30),10-K219)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N219" s="36" t="n"/>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="M220" s="39">
         <f>IF(OR(B220="",L220="Feito",L220="Cancelado",L220="Sem prazo",L220="Depois"),0,IF(L220="Atrasada",2000,IF(L220="Hoje",1500,500))+F220*G220*100+IF(K220&lt;0,MIN(-K220,30),10-K220)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N220" s="36" t="n"/>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="M221" s="39">
         <f>IF(OR(B221="",L221="Feito",L221="Cancelado",L221="Sem prazo",L221="Depois"),0,IF(L221="Atrasada",2000,IF(L221="Hoje",1500,500))+F221*G221*100+IF(K221&lt;0,MIN(-K221,30),10-K221)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N221" s="36" t="n"/>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="M222" s="39">
         <f>IF(OR(B222="",L222="Feito",L222="Cancelado",L222="Sem prazo",L222="Depois"),0,IF(L222="Atrasada",2000,IF(L222="Hoje",1500,500))+F222*G222*100+IF(K222&lt;0,MIN(-K222,30),10-K222)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N222" s="36" t="n"/>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="M223" s="39">
         <f>IF(OR(B223="",L223="Feito",L223="Cancelado",L223="Sem prazo",L223="Depois"),0,IF(L223="Atrasada",2000,IF(L223="Hoje",1500,500))+F223*G223*100+IF(K223&lt;0,MIN(-K223,30),10-K223)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N223" s="36" t="n"/>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M224" s="39">
         <f>IF(OR(B224="",L224="Feito",L224="Cancelado",L224="Sem prazo",L224="Depois"),0,IF(L224="Atrasada",2000,IF(L224="Hoje",1500,500))+F224*G224*100+IF(K224&lt;0,MIN(-K224,30),10-K224)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N224" s="36" t="n"/>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="M225" s="39">
         <f>IF(OR(B225="",L225="Feito",L225="Cancelado",L225="Sem prazo",L225="Depois"),0,IF(L225="Atrasada",2000,IF(L225="Hoje",1500,500))+F225*G225*100+IF(K225&lt;0,MIN(-K225,30),10-K225)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N225" s="36" t="n"/>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M226" s="39">
         <f>IF(OR(B226="",L226="Feito",L226="Cancelado",L226="Sem prazo",L226="Depois"),0,IF(L226="Atrasada",2000,IF(L226="Hoje",1500,500))+F226*G226*100+IF(K226&lt;0,MIN(-K226,30),10-K226)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N226" s="36" t="n"/>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="M227" s="39">
         <f>IF(OR(B227="",L227="Feito",L227="Cancelado",L227="Sem prazo",L227="Depois"),0,IF(L227="Atrasada",2000,IF(L227="Hoje",1500,500))+F227*G227*100+IF(K227&lt;0,MIN(-K227,30),10-K227)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N227" s="36" t="n"/>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="M228" s="39">
         <f>IF(OR(B228="",L228="Feito",L228="Cancelado",L228="Sem prazo",L228="Depois"),0,IF(L228="Atrasada",2000,IF(L228="Hoje",1500,500))+F228*G228*100+IF(K228&lt;0,MIN(-K228,30),10-K228)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N228" s="36" t="n"/>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="M229" s="39">
         <f>IF(OR(B229="",L229="Feito",L229="Cancelado",L229="Sem prazo",L229="Depois"),0,IF(L229="Atrasada",2000,IF(L229="Hoje",1500,500))+F229*G229*100+IF(K229&lt;0,MIN(-K229,30),10-K229)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N229" s="36" t="n"/>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="M230" s="39">
         <f>IF(OR(B230="",L230="Feito",L230="Cancelado",L230="Sem prazo",L230="Depois"),0,IF(L230="Atrasada",2000,IF(L230="Hoje",1500,500))+F230*G230*100+IF(K230&lt;0,MIN(-K230,30),10-K230)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N230" s="36" t="n"/>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="M231" s="39">
         <f>IF(OR(B231="",L231="Feito",L231="Cancelado",L231="Sem prazo",L231="Depois"),0,IF(L231="Atrasada",2000,IF(L231="Hoje",1500,500))+F231*G231*100+IF(K231&lt;0,MIN(-K231,30),10-K231)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N231" s="36" t="n"/>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="M232" s="39">
         <f>IF(OR(B232="",L232="Feito",L232="Cancelado",L232="Sem prazo",L232="Depois"),0,IF(L232="Atrasada",2000,IF(L232="Hoje",1500,500))+F232*G232*100+IF(K232&lt;0,MIN(-K232,30),10-K232)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N232" s="36" t="n"/>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="M233" s="39">
         <f>IF(OR(B233="",L233="Feito",L233="Cancelado",L233="Sem prazo",L233="Depois"),0,IF(L233="Atrasada",2000,IF(L233="Hoje",1500,500))+F233*G233*100+IF(K233&lt;0,MIN(-K233,30),10-K233)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N233" s="36" t="n"/>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="M234" s="39">
         <f>IF(OR(B234="",L234="Feito",L234="Cancelado",L234="Sem prazo",L234="Depois"),0,IF(L234="Atrasada",2000,IF(L234="Hoje",1500,500))+F234*G234*100+IF(K234&lt;0,MIN(-K234,30),10-K234)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N234" s="36" t="n"/>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="M235" s="39">
         <f>IF(OR(B235="",L235="Feito",L235="Cancelado",L235="Sem prazo",L235="Depois"),0,IF(L235="Atrasada",2000,IF(L235="Hoje",1500,500))+F235*G235*100+IF(K235&lt;0,MIN(-K235,30),10-K235)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N235" s="36" t="n"/>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M236" s="39">
         <f>IF(OR(B236="",L236="Feito",L236="Cancelado",L236="Sem prazo",L236="Depois"),0,IF(L236="Atrasada",2000,IF(L236="Hoje",1500,500))+F236*G236*100+IF(K236&lt;0,MIN(-K236,30),10-K236)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N236" s="36" t="n"/>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="M237" s="39">
         <f>IF(OR(B237="",L237="Feito",L237="Cancelado",L237="Sem prazo",L237="Depois"),0,IF(L237="Atrasada",2000,IF(L237="Hoje",1500,500))+F237*G237*100+IF(K237&lt;0,MIN(-K237,30),10-K237)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N237" s="36" t="n"/>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="M238" s="39">
         <f>IF(OR(B238="",L238="Feito",L238="Cancelado",L238="Sem prazo",L238="Depois"),0,IF(L238="Atrasada",2000,IF(L238="Hoje",1500,500))+F238*G238*100+IF(K238&lt;0,MIN(-K238,30),10-K238)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N238" s="36" t="n"/>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="M239" s="39">
         <f>IF(OR(B239="",L239="Feito",L239="Cancelado",L239="Sem prazo",L239="Depois"),0,IF(L239="Atrasada",2000,IF(L239="Hoje",1500,500))+F239*G239*100+IF(K239&lt;0,MIN(-K239,30),10-K239)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N239" s="36" t="n"/>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="M240" s="39">
         <f>IF(OR(B240="",L240="Feito",L240="Cancelado",L240="Sem prazo",L240="Depois"),0,IF(L240="Atrasada",2000,IF(L240="Hoje",1500,500))+F240*G240*100+IF(K240&lt;0,MIN(-K240,30),10-K240)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N240" s="36" t="n"/>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="M241" s="39">
         <f>IF(OR(B241="",L241="Feito",L241="Cancelado",L241="Sem prazo",L241="Depois"),0,IF(L241="Atrasada",2000,IF(L241="Hoje",1500,500))+F241*G241*100+IF(K241&lt;0,MIN(-K241,30),10-K241)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N241" s="36" t="n"/>
     </row>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="M242" s="39">
         <f>IF(OR(B242="",L242="Feito",L242="Cancelado",L242="Sem prazo",L242="Depois"),0,IF(L242="Atrasada",2000,IF(L242="Hoje",1500,500))+F242*G242*100+IF(K242&lt;0,MIN(-K242,30),10-K242)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N242" s="36" t="n"/>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="M243" s="39">
         <f>IF(OR(B243="",L243="Feito",L243="Cancelado",L243="Sem prazo",L243="Depois"),0,IF(L243="Atrasada",2000,IF(L243="Hoje",1500,500))+F243*G243*100+IF(K243&lt;0,MIN(-K243,30),10-K243)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N243" s="36" t="n"/>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="M244" s="39">
         <f>IF(OR(B244="",L244="Feito",L244="Cancelado",L244="Sem prazo",L244="Depois"),0,IF(L244="Atrasada",2000,IF(L244="Hoje",1500,500))+F244*G244*100+IF(K244&lt;0,MIN(-K244,30),10-K244)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N244" s="36" t="n"/>
     </row>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="M245" s="39">
         <f>IF(OR(B245="",L245="Feito",L245="Cancelado",L245="Sem prazo",L245="Depois"),0,IF(L245="Atrasada",2000,IF(L245="Hoje",1500,500))+F245*G245*100+IF(K245&lt;0,MIN(-K245,30),10-K245)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N245" s="36" t="n"/>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="M246" s="39">
         <f>IF(OR(B246="",L246="Feito",L246="Cancelado",L246="Sem prazo",L246="Depois"),0,IF(L246="Atrasada",2000,IF(L246="Hoje",1500,500))+F246*G246*100+IF(K246&lt;0,MIN(-K246,30),10-K246)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N246" s="36" t="n"/>
     </row>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="M247" s="39">
         <f>IF(OR(B247="",L247="Feito",L247="Cancelado",L247="Sem prazo",L247="Depois"),0,IF(L247="Atrasada",2000,IF(L247="Hoje",1500,500))+F247*G247*100+IF(K247&lt;0,MIN(-K247,30),10-K247)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N247" s="36" t="n"/>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M248" s="39">
         <f>IF(OR(B248="",L248="Feito",L248="Cancelado",L248="Sem prazo",L248="Depois"),0,IF(L248="Atrasada",2000,IF(L248="Hoje",1500,500))+F248*G248*100+IF(K248&lt;0,MIN(-K248,30),10-K248)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N248" s="36" t="n"/>
     </row>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="M249" s="39">
         <f>IF(OR(B249="",L249="Feito",L249="Cancelado",L249="Sem prazo",L249="Depois"),0,IF(L249="Atrasada",2000,IF(L249="Hoje",1500,500))+F249*G249*100+IF(K249&lt;0,MIN(-K249,30),10-K249)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N249" s="36" t="n"/>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="M250" s="39">
         <f>IF(OR(B250="",L250="Feito",L250="Cancelado",L250="Sem prazo",L250="Depois"),0,IF(L250="Atrasada",2000,IF(L250="Hoje",1500,500))+F250*G250*100+IF(K250&lt;0,MIN(-K250,30),10-K250)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N250" s="36" t="n"/>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="M251" s="39">
         <f>IF(OR(B251="",L251="Feito",L251="Cancelado",L251="Sem prazo",L251="Depois"),0,IF(L251="Atrasada",2000,IF(L251="Hoje",1500,500))+F251*G251*100+IF(K251&lt;0,MIN(-K251,30),10-K251)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N251" s="36" t="n"/>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="M252" s="39">
         <f>IF(OR(B252="",L252="Feito",L252="Cancelado",L252="Sem prazo",L252="Depois"),0,IF(L252="Atrasada",2000,IF(L252="Hoje",1500,500))+F252*G252*100+IF(K252&lt;0,MIN(-K252,30),10-K252)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N252" s="36" t="n"/>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="M253" s="39">
         <f>IF(OR(B253="",L253="Feito",L253="Cancelado",L253="Sem prazo",L253="Depois"),0,IF(L253="Atrasada",2000,IF(L253="Hoje",1500,500))+F253*G253*100+IF(K253&lt;0,MIN(-K253,30),10-K253)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N253" s="36" t="n"/>
     </row>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="M254" s="39">
         <f>IF(OR(B254="",L254="Feito",L254="Cancelado",L254="Sem prazo",L254="Depois"),0,IF(L254="Atrasada",2000,IF(L254="Hoje",1500,500))+F254*G254*100+IF(K254&lt;0,MIN(-K254,30),10-K254)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N254" s="36" t="n"/>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="M255" s="39">
         <f>IF(OR(B255="",L255="Feito",L255="Cancelado",L255="Sem prazo",L255="Depois"),0,IF(L255="Atrasada",2000,IF(L255="Hoje",1500,500))+F255*G255*100+IF(K255&lt;0,MIN(-K255,30),10-K255)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N255" s="36" t="n"/>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M256" s="39">
         <f>IF(OR(B256="",L256="Feito",L256="Cancelado",L256="Sem prazo",L256="Depois"),0,IF(L256="Atrasada",2000,IF(L256="Hoje",1500,500))+F256*G256*100+IF(K256&lt;0,MIN(-K256,30),10-K256)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N256" s="36" t="n"/>
     </row>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="M257" s="39">
         <f>IF(OR(B257="",L257="Feito",L257="Cancelado",L257="Sem prazo",L257="Depois"),0,IF(L257="Atrasada",2000,IF(L257="Hoje",1500,500))+F257*G257*100+IF(K257&lt;0,MIN(-K257,30),10-K257)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N257" s="36" t="n"/>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="M258" s="39">
         <f>IF(OR(B258="",L258="Feito",L258="Cancelado",L258="Sem prazo",L258="Depois"),0,IF(L258="Atrasada",2000,IF(L258="Hoje",1500,500))+F258*G258*100+IF(K258&lt;0,MIN(-K258,30),10-K258)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N258" s="36" t="n"/>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="M259" s="39">
         <f>IF(OR(B259="",L259="Feito",L259="Cancelado",L259="Sem prazo",L259="Depois"),0,IF(L259="Atrasada",2000,IF(L259="Hoje",1500,500))+F259*G259*100+IF(K259&lt;0,MIN(-K259,30),10-K259)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N259" s="36" t="n"/>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="M260" s="39">
         <f>IF(OR(B260="",L260="Feito",L260="Cancelado",L260="Sem prazo",L260="Depois"),0,IF(L260="Atrasada",2000,IF(L260="Hoje",1500,500))+F260*G260*100+IF(K260&lt;0,MIN(-K260,30),10-K260)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N260" s="36" t="n"/>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="M261" s="39">
         <f>IF(OR(B261="",L261="Feito",L261="Cancelado",L261="Sem prazo",L261="Depois"),0,IF(L261="Atrasada",2000,IF(L261="Hoje",1500,500))+F261*G261*100+IF(K261&lt;0,MIN(-K261,30),10-K261)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N261" s="36" t="n"/>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="M262" s="39">
         <f>IF(OR(B262="",L262="Feito",L262="Cancelado",L262="Sem prazo",L262="Depois"),0,IF(L262="Atrasada",2000,IF(L262="Hoje",1500,500))+F262*G262*100+IF(K262&lt;0,MIN(-K262,30),10-K262)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N262" s="36" t="n"/>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="M263" s="39">
         <f>IF(OR(B263="",L263="Feito",L263="Cancelado",L263="Sem prazo",L263="Depois"),0,IF(L263="Atrasada",2000,IF(L263="Hoje",1500,500))+F263*G263*100+IF(K263&lt;0,MIN(-K263,30),10-K263)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N263" s="36" t="n"/>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="M264" s="39">
         <f>IF(OR(B264="",L264="Feito",L264="Cancelado",L264="Sem prazo",L264="Depois"),0,IF(L264="Atrasada",2000,IF(L264="Hoje",1500,500))+F264*G264*100+IF(K264&lt;0,MIN(-K264,30),10-K264)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N264" s="36" t="n"/>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="M265" s="39">
         <f>IF(OR(B265="",L265="Feito",L265="Cancelado",L265="Sem prazo",L265="Depois"),0,IF(L265="Atrasada",2000,IF(L265="Hoje",1500,500))+F265*G265*100+IF(K265&lt;0,MIN(-K265,30),10-K265)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N265" s="36" t="n"/>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="M266" s="39">
         <f>IF(OR(B266="",L266="Feito",L266="Cancelado",L266="Sem prazo",L266="Depois"),0,IF(L266="Atrasada",2000,IF(L266="Hoje",1500,500))+F266*G266*100+IF(K266&lt;0,MIN(-K266,30),10-K266)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N266" s="36" t="n"/>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="M267" s="39">
         <f>IF(OR(B267="",L267="Feito",L267="Cancelado",L267="Sem prazo",L267="Depois"),0,IF(L267="Atrasada",2000,IF(L267="Hoje",1500,500))+F267*G267*100+IF(K267&lt;0,MIN(-K267,30),10-K267)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N267" s="36" t="n"/>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="M268" s="39">
         <f>IF(OR(B268="",L268="Feito",L268="Cancelado",L268="Sem prazo",L268="Depois"),0,IF(L268="Atrasada",2000,IF(L268="Hoje",1500,500))+F268*G268*100+IF(K268&lt;0,MIN(-K268,30),10-K268)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N268" s="36" t="n"/>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="M269" s="39">
         <f>IF(OR(B269="",L269="Feito",L269="Cancelado",L269="Sem prazo",L269="Depois"),0,IF(L269="Atrasada",2000,IF(L269="Hoje",1500,500))+F269*G269*100+IF(K269&lt;0,MIN(-K269,30),10-K269)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N269" s="36" t="n"/>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M270" s="39">
         <f>IF(OR(B270="",L270="Feito",L270="Cancelado",L270="Sem prazo",L270="Depois"),0,IF(L270="Atrasada",2000,IF(L270="Hoje",1500,500))+F270*G270*100+IF(K270&lt;0,MIN(-K270,30),10-K270)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N270" s="36" t="n"/>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M271" s="39">
         <f>IF(OR(B271="",L271="Feito",L271="Cancelado",L271="Sem prazo",L271="Depois"),0,IF(L271="Atrasada",2000,IF(L271="Hoje",1500,500))+F271*G271*100+IF(K271&lt;0,MIN(-K271,30),10-K271)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N271" s="36" t="n"/>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="M272" s="39">
         <f>IF(OR(B272="",L272="Feito",L272="Cancelado",L272="Sem prazo",L272="Depois"),0,IF(L272="Atrasada",2000,IF(L272="Hoje",1500,500))+F272*G272*100+IF(K272&lt;0,MIN(-K272,30),10-K272)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N272" s="36" t="n"/>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="M273" s="39">
         <f>IF(OR(B273="",L273="Feito",L273="Cancelado",L273="Sem prazo",L273="Depois"),0,IF(L273="Atrasada",2000,IF(L273="Hoje",1500,500))+F273*G273*100+IF(K273&lt;0,MIN(-K273,30),10-K273)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N273" s="36" t="n"/>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="M274" s="39">
         <f>IF(OR(B274="",L274="Feito",L274="Cancelado",L274="Sem prazo",L274="Depois"),0,IF(L274="Atrasada",2000,IF(L274="Hoje",1500,500))+F274*G274*100+IF(K274&lt;0,MIN(-K274,30),10-K274)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N274" s="36" t="n"/>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="M275" s="39">
         <f>IF(OR(B275="",L275="Feito",L275="Cancelado",L275="Sem prazo",L275="Depois"),0,IF(L275="Atrasada",2000,IF(L275="Hoje",1500,500))+F275*G275*100+IF(K275&lt;0,MIN(-K275,30),10-K275)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N275" s="36" t="n"/>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="M276" s="39">
         <f>IF(OR(B276="",L276="Feito",L276="Cancelado",L276="Sem prazo",L276="Depois"),0,IF(L276="Atrasada",2000,IF(L276="Hoje",1500,500))+F276*G276*100+IF(K276&lt;0,MIN(-K276,30),10-K276)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N276" s="36" t="n"/>
     </row>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="M277" s="39">
         <f>IF(OR(B277="",L277="Feito",L277="Cancelado",L277="Sem prazo",L277="Depois"),0,IF(L277="Atrasada",2000,IF(L277="Hoje",1500,500))+F277*G277*100+IF(K277&lt;0,MIN(-K277,30),10-K277)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N277" s="36" t="n"/>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="M278" s="39">
         <f>IF(OR(B278="",L278="Feito",L278="Cancelado",L278="Sem prazo",L278="Depois"),0,IF(L278="Atrasada",2000,IF(L278="Hoje",1500,500))+F278*G278*100+IF(K278&lt;0,MIN(-K278,30),10-K278)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N278" s="36" t="n"/>
     </row>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="M279" s="39">
         <f>IF(OR(B279="",L279="Feito",L279="Cancelado",L279="Sem prazo",L279="Depois"),0,IF(L279="Atrasada",2000,IF(L279="Hoje",1500,500))+F279*G279*100+IF(K279&lt;0,MIN(-K279,30),10-K279)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N279" s="36" t="n"/>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="M280" s="39">
         <f>IF(OR(B280="",L280="Feito",L280="Cancelado",L280="Sem prazo",L280="Depois"),0,IF(L280="Atrasada",2000,IF(L280="Hoje",1500,500))+F280*G280*100+IF(K280&lt;0,MIN(-K280,30),10-K280)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N280" s="36" t="n"/>
     </row>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="M281" s="39">
         <f>IF(OR(B281="",L281="Feito",L281="Cancelado",L281="Sem prazo",L281="Depois"),0,IF(L281="Atrasada",2000,IF(L281="Hoje",1500,500))+F281*G281*100+IF(K281&lt;0,MIN(-K281,30),10-K281)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N281" s="36" t="n"/>
     </row>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="M282" s="39">
         <f>IF(OR(B282="",L282="Feito",L282="Cancelado",L282="Sem prazo",L282="Depois"),0,IF(L282="Atrasada",2000,IF(L282="Hoje",1500,500))+F282*G282*100+IF(K282&lt;0,MIN(-K282,30),10-K282)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N282" s="36" t="n"/>
     </row>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="M283" s="39">
         <f>IF(OR(B283="",L283="Feito",L283="Cancelado",L283="Sem prazo",L283="Depois"),0,IF(L283="Atrasada",2000,IF(L283="Hoje",1500,500))+F283*G283*100+IF(K283&lt;0,MIN(-K283,30),10-K283)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N283" s="36" t="n"/>
     </row>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="M284" s="39">
         <f>IF(OR(B284="",L284="Feito",L284="Cancelado",L284="Sem prazo",L284="Depois"),0,IF(L284="Atrasada",2000,IF(L284="Hoje",1500,500))+F284*G284*100+IF(K284&lt;0,MIN(-K284,30),10-K284)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N284" s="36" t="n"/>
     </row>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="M285" s="39">
         <f>IF(OR(B285="",L285="Feito",L285="Cancelado",L285="Sem prazo",L285="Depois"),0,IF(L285="Atrasada",2000,IF(L285="Hoje",1500,500))+F285*G285*100+IF(K285&lt;0,MIN(-K285,30),10-K285)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N285" s="36" t="n"/>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="M286" s="39">
         <f>IF(OR(B286="",L286="Feito",L286="Cancelado",L286="Sem prazo",L286="Depois"),0,IF(L286="Atrasada",2000,IF(L286="Hoje",1500,500))+F286*G286*100+IF(K286&lt;0,MIN(-K286,30),10-K286)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N286" s="36" t="n"/>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="M287" s="39">
         <f>IF(OR(B287="",L287="Feito",L287="Cancelado",L287="Sem prazo",L287="Depois"),0,IF(L287="Atrasada",2000,IF(L287="Hoje",1500,500))+F287*G287*100+IF(K287&lt;0,MIN(-K287,30),10-K287)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N287" s="36" t="n"/>
     </row>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="M288" s="39">
         <f>IF(OR(B288="",L288="Feito",L288="Cancelado",L288="Sem prazo",L288="Depois"),0,IF(L288="Atrasada",2000,IF(L288="Hoje",1500,500))+F288*G288*100+IF(K288&lt;0,MIN(-K288,30),10-K288)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N288" s="36" t="n"/>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="M289" s="39">
         <f>IF(OR(B289="",L289="Feito",L289="Cancelado",L289="Sem prazo",L289="Depois"),0,IF(L289="Atrasada",2000,IF(L289="Hoje",1500,500))+F289*G289*100+IF(K289&lt;0,MIN(-K289,30),10-K289)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N289" s="36" t="n"/>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="M290" s="39">
         <f>IF(OR(B290="",L290="Feito",L290="Cancelado",L290="Sem prazo",L290="Depois"),0,IF(L290="Atrasada",2000,IF(L290="Hoje",1500,500))+F290*G290*100+IF(K290&lt;0,MIN(-K290,30),10-K290)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N290" s="36" t="n"/>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M291" s="39">
         <f>IF(OR(B291="",L291="Feito",L291="Cancelado",L291="Sem prazo",L291="Depois"),0,IF(L291="Atrasada",2000,IF(L291="Hoje",1500,500))+F291*G291*100+IF(K291&lt;0,MIN(-K291,30),10-K291)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N291" s="36" t="n"/>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="M292" s="39">
         <f>IF(OR(B292="",L292="Feito",L292="Cancelado",L292="Sem prazo",L292="Depois"),0,IF(L292="Atrasada",2000,IF(L292="Hoje",1500,500))+F292*G292*100+IF(K292&lt;0,MIN(-K292,30),10-K292)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N292" s="36" t="n"/>
     </row>
@@ -11721,7 +11721,7 @@
       </c>
       <c r="M293" s="39">
         <f>IF(OR(B293="",L293="Feito",L293="Cancelado",L293="Sem prazo",L293="Depois"),0,IF(L293="Atrasada",2000,IF(L293="Hoje",1500,500))+F293*G293*100+IF(K293&lt;0,MIN(-K293,30),10-K293)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N293" s="36" t="n"/>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="M294" s="39">
         <f>IF(OR(B294="",L294="Feito",L294="Cancelado",L294="Sem prazo",L294="Depois"),0,IF(L294="Atrasada",2000,IF(L294="Hoje",1500,500))+F294*G294*100+IF(K294&lt;0,MIN(-K294,30),10-K294)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N294" s="36" t="n"/>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="M295" s="39">
         <f>IF(OR(B295="",L295="Feito",L295="Cancelado",L295="Sem prazo",L295="Depois"),0,IF(L295="Atrasada",2000,IF(L295="Hoje",1500,500))+F295*G295*100+IF(K295&lt;0,MIN(-K295,30),10-K295)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N295" s="36" t="n"/>
     </row>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="M296" s="39">
         <f>IF(OR(B296="",L296="Feito",L296="Cancelado",L296="Sem prazo",L296="Depois"),0,IF(L296="Atrasada",2000,IF(L296="Hoje",1500,500))+F296*G296*100+IF(K296&lt;0,MIN(-K296,30),10-K296)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N296" s="36" t="n"/>
     </row>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="M297" s="39">
         <f>IF(OR(B297="",L297="Feito",L297="Cancelado",L297="Sem prazo",L297="Depois"),0,IF(L297="Atrasada",2000,IF(L297="Hoje",1500,500))+F297*G297*100+IF(K297&lt;0,MIN(-K297,30),10-K297)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N297" s="36" t="n"/>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M298" s="39">
         <f>IF(OR(B298="",L298="Feito",L298="Cancelado",L298="Sem prazo",L298="Depois"),0,IF(L298="Atrasada",2000,IF(L298="Hoje",1500,500))+F298*G298*100+IF(K298&lt;0,MIN(-K298,30),10-K298)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N298" s="36" t="n"/>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="M299" s="39">
         <f>IF(OR(B299="",L299="Feito",L299="Cancelado",L299="Sem prazo",L299="Depois"),0,IF(L299="Atrasada",2000,IF(L299="Hoje",1500,500))+F299*G299*100+IF(K299&lt;0,MIN(-K299,30),10-K299)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N299" s="36" t="n"/>
     </row>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="M300" s="39">
         <f>IF(OR(B300="",L300="Feito",L300="Cancelado",L300="Sem prazo",L300="Depois"),0,IF(L300="Atrasada",2000,IF(L300="Hoje",1500,500))+F300*G300*100+IF(K300&lt;0,MIN(-K300,30),10-K300)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N300" s="36" t="n"/>
     </row>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="M301" s="39">
         <f>IF(OR(B301="",L301="Feito",L301="Cancelado",L301="Sem prazo",L301="Depois"),0,IF(L301="Atrasada",2000,IF(L301="Hoje",1500,500))+F301*G301*100+IF(K301&lt;0,MIN(-K301,30),10-K301)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N301" s="36" t="n"/>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="M302" s="39">
         <f>IF(OR(B302="",L302="Feito",L302="Cancelado",L302="Sem prazo",L302="Depois"),0,IF(L302="Atrasada",2000,IF(L302="Hoje",1500,500))+F302*G302*100+IF(K302&lt;0,MIN(-K302,30),10-K302)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N302" s="36" t="n"/>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="M303" s="39">
         <f>IF(OR(B303="",L303="Feito",L303="Cancelado",L303="Sem prazo",L303="Depois"),0,IF(L303="Atrasada",2000,IF(L303="Hoje",1500,500))+F303*G303*100+IF(K303&lt;0,MIN(-K303,30),10-K303)-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N303" s="36" t="n"/>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
@@ -12058,22 +12058,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="D4:D303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D4:D303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$9,0,0,MAX(1,COUNTA(Config!$B$9:$B$16)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:G303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:G303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$D$9:$D$12</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:C303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C4:C303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$9,0,0,MAX(1,COUNTA(Config!$F$9:$F$16)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="E4:E303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H303" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H4:H303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
@@ -945,7 +945,7 @@
     <row r="2">
       <c r="A2" s="7" t="str">
         <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v>Painel de 17/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
+        <v>Painel de 18/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46280.0</v>
+        <v>46281.0</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1450,11 +1450,11 @@
     <row r="25">
       <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qui</v>
+        <v>sex</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1478,11 +1478,11 @@
     <row r="26">
       <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sex</v>
+        <v>sáb</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1506,11 +1506,11 @@
     <row r="27">
       <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sáb</v>
+        <v>dom</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1534,11 +1534,11 @@
     <row r="28">
       <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>dom</v>
+        <v>seg</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1562,11 +1562,11 @@
     <row r="29">
       <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>seg</v>
+        <v>ter</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1590,11 +1590,11 @@
     <row r="30">
       <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>ter</v>
+        <v>qua</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1618,11 +1618,11 @@
     <row r="31">
       <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qua</v>
+        <v>qui</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v>46281.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v>46280.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v>46284.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v>46287.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v>46289.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v>46273.0</v>
+        <v>46274.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v>46292.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v>46295.0</v>
+        <v>46296.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v>46298.0</v>
+        <v>46299.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v>46279.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v>46276.0</v>
+        <v>46277.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/entrega/01-semana-organizada.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload do arquivo no Google Drive e abra com o Google Sheets. Tudo funciona: listas, cores e fórmulas.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Listas, cores e fórmulas funcionam.</t>
         </is>
       </c>
     </row>
@@ -944,8 +944,8 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="str">
-        <f>"Painel de "&amp;TEXT(Config!B4,"dd/mm/yyyy")&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
-        <v>Painel de 18/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
+        <f>"Painel de "&amp;TEXT(DAY(Config!B4),"00")&amp;"/"&amp;TEXT(MONTH(Config!B4),"00")&amp;"/"&amp;YEAR(Config!B4)&amp;". Nada para preencher aqui: tudo vem da aba Tarefas."</f>
+        <v>Painel de 24/09/2026. Nada para preencher aqui: tudo vem da aba Tarefas.</v>
       </c>
     </row>
     <row r="4">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46282.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,1)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,1),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C11" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46283.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,2)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,2),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C12" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46281.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,3)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,3),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C13" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,4)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,4),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C14" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,5)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,5),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C15" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46292.0</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,6)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,6),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C16" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46293.0</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,7)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,7),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C17" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,8)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,8),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C18" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46285.0</v>
+        <v>46291.0</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,9)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,9),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C19" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46289.0</v>
+        <v>46295.0</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,10)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,10),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C20" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46287.0</v>
+        <v>46293.0</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,11)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,11),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C21" s="25">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$E$4:$E$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46294.0</v>
       </c>
       <c r="D21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Tarefas!$M$4:$M$303,12)&gt;0,INDEX(Tarefas!$L$4:$L$303,MATCH(LARGE(Tarefas!$M$4:$M$303,12),Tarefas!$M$4:$M$303,0)),""),"")</f>
@@ -1450,11 +1450,11 @@
     <row r="25">
       <c r="A25" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B25),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sex</v>
+        <v>qui</v>
       </c>
       <c r="B25" s="25">
         <f>Config!$B$4+0</f>
-        <v>46283.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C25" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B25,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1478,11 +1478,11 @@
     <row r="26">
       <c r="A26" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B26),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>sáb</v>
+        <v>sex</v>
       </c>
       <c r="B26" s="25">
         <f>Config!$B$4+1</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="C26" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B26,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1506,11 +1506,11 @@
     <row r="27">
       <c r="A27" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B27),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>dom</v>
+        <v>sáb</v>
       </c>
       <c r="B27" s="25">
         <f>Config!$B$4+2</f>
-        <v>46285.0</v>
+        <v>46291.0</v>
       </c>
       <c r="C27" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B27,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1534,11 +1534,11 @@
     <row r="28">
       <c r="A28" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B28),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>seg</v>
+        <v>dom</v>
       </c>
       <c r="B28" s="25">
         <f>Config!$B$4+3</f>
-        <v>46286.0</v>
+        <v>46292.0</v>
       </c>
       <c r="C28" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B28,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1562,11 +1562,11 @@
     <row r="29">
       <c r="A29" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B29),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>ter</v>
+        <v>seg</v>
       </c>
       <c r="B29" s="25">
         <f>Config!$B$4+4</f>
-        <v>46287.0</v>
+        <v>46293.0</v>
       </c>
       <c r="C29" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B29,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1590,11 +1590,11 @@
     <row r="30">
       <c r="A30" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B30),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qua</v>
+        <v>ter</v>
       </c>
       <c r="B30" s="25">
         <f>Config!$B$4+5</f>
-        <v>46288.0</v>
+        <v>46294.0</v>
       </c>
       <c r="C30" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B30,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1618,11 +1618,11 @@
     <row r="31">
       <c r="A31" s="23" t="str">
         <f>CHOOSE(WEEKDAY(B31),"dom","seg","ter","qua","qui","sex","sáb")</f>
-        <v>qui</v>
+        <v>qua</v>
       </c>
       <c r="B31" s="25">
         <f>Config!$B$4+6</f>
-        <v>46289.0</v>
+        <v>46295.0</v>
       </c>
       <c r="C31" s="23">
         <f>COUNTIFS(Tarefas!$E$4:$E$303,B31,Tarefas!$I$4:$I$303,"&lt;&gt;Feito",Tarefas!$I$4:$I$303,"&lt;&gt;Cancelado",Tarefas!$B$4:$B$303,"&lt;&gt;")</f>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B4" s="32">
         <f>TODAY()</f>
-        <v>46283.0</v>
+        <v>46289.0</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="E4" s="37">
         <f>TODAY()-1</f>
-        <v>46282.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F4" s="38" t="n">
         <v>3</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E5" s="37">
         <f>TODAY()</f>
-        <v>46283.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>3</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E6" s="37">
         <f>TODAY()-2</f>
-        <v>46281.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E7" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>3</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E8" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E9" s="37">
         <f>TODAY()+1</f>
-        <v>46284.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F9" s="38" t="n">
         <v>2</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E10" s="37">
         <f>TODAY()+2</f>
-        <v>46285.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F10" s="38" t="n">
         <v>2</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E11" s="37">
         <f>TODAY()+3</f>
-        <v>46286.0</v>
+        <v>46292.0</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>3</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E12" s="37">
         <f>TODAY()+4</f>
-        <v>46287.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E13" s="37">
         <f>TODAY()+4</f>
-        <v>46287.0</v>
+        <v>46293.0</v>
       </c>
       <c r="F13" s="38" t="n">
         <v>3</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E14" s="37">
         <f>TODAY()+5</f>
-        <v>46288.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F14" s="38" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E15" s="37">
         <f>TODAY()+6</f>
-        <v>46289.0</v>
+        <v>46295.0</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>3</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E16" s="37">
         <f>TODAY()+7</f>
-        <v>46290.0</v>
+        <v>46296.0</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>2</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E17" s="37">
         <f>TODAY()-9</f>
-        <v>46274.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F17" s="38" t="n">
         <v>3</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E18" s="37">
         <f>TODAY()+10</f>
-        <v>46293.0</v>
+        <v>46299.0</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E19" s="37">
         <f>TODAY()+13</f>
-        <v>46296.0</v>
+        <v>46302.0</v>
       </c>
       <c r="F19" s="38" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E20" s="37">
         <f>TODAY()+16</f>
-        <v>46299.0</v>
+        <v>46305.0</v>
       </c>
       <c r="F20" s="38" t="n">
         <v>3</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E21" s="37">
         <f>TODAY()-3</f>
-        <v>46280.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E23" s="37">
         <f>TODAY()-6</f>
-        <v>46277.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>2</v>
